--- a/docs/estimation/SVT_transformation_effort_estimate.xlsx
+++ b/docs/estimation/SVT_transformation_effort_estimate.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22476" windowHeight="8532" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22476" windowHeight="8532"/>
   </bookViews>
   <sheets>
     <sheet name="Этапы" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Задачи_бэклога!$A$1:$I$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Нормы_и_допущения!$A$1:$C$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Подзадачи!$A$1:$L$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Подзадачи!$A$1:$M$232</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Сделано_vs_Остаток!$A$1:$E$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Этапы!$A$1:$J$16</definedName>
   </definedNames>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="487">
   <si>
     <t>Этап</t>
   </si>
@@ -1488,13 +1488,16 @@
   </si>
   <si>
     <t>Задача</t>
+  </si>
+  <si>
+    <t>Без агента, ч.д</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1513,8 +1516,52 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1529,6 +1576,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1556,10 +1608,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1571,8 +1624,19 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1924,10 +1988,10 @@
       <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="9">
         <v>46</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="11">
         <v>29</v>
       </c>
       <c r="D2" s="2">
@@ -1956,10 +2020,10 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="9">
         <v>149</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="11">
         <v>90.4</v>
       </c>
       <c r="D3" s="2">
@@ -1988,10 +2052,10 @@
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="9">
         <v>373</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="11">
         <v>140.5</v>
       </c>
       <c r="D4" s="2">
@@ -2020,10 +2084,10 @@
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="9">
         <v>61</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="11">
         <v>28.5</v>
       </c>
       <c r="D5" s="2">
@@ -2052,10 +2116,10 @@
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="9">
         <v>35</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="11">
         <v>19.5</v>
       </c>
       <c r="D6" s="2">
@@ -2084,10 +2148,10 @@
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="9">
         <v>116.5</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="11">
         <v>70.5</v>
       </c>
       <c r="D7" s="2">
@@ -2116,10 +2180,10 @@
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="9">
         <v>547.5</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="11">
         <v>246.3</v>
       </c>
       <c r="D8" s="2">
@@ -2148,10 +2212,10 @@
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="9">
         <v>64</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="11">
         <v>40.9</v>
       </c>
       <c r="D9" s="2">
@@ -2180,10 +2244,10 @@
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="9">
         <v>228.5</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="11">
         <v>100.3</v>
       </c>
       <c r="D10" s="2">
@@ -2212,10 +2276,10 @@
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="9">
         <v>66</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="11">
         <v>37</v>
       </c>
       <c r="D11" s="2">
@@ -2244,10 +2308,10 @@
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="9">
         <v>37.5</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="11">
         <v>21.8</v>
       </c>
       <c r="D12" s="2">
@@ -2276,10 +2340,10 @@
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="9">
         <v>86</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="11">
         <v>42</v>
       </c>
       <c r="D13" s="2">
@@ -2308,10 +2372,10 @@
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="9">
         <v>122</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="11">
         <v>62.5</v>
       </c>
       <c r="D14" s="2">
@@ -2340,10 +2404,10 @@
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="9">
         <v>43</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="11">
         <v>29</v>
       </c>
       <c r="D15" s="2">
@@ -2372,10 +2436,10 @@
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="10">
         <v>1975</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="12">
         <v>958.2</v>
       </c>
       <c r="D16" s="3">
@@ -3822,7 +3886,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L232"/>
+  <dimension ref="A1:M232"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="6" customWidth="1"/>
@@ -3831,15 +3895,15 @@
     <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="55" customWidth="1"/>
+    <col min="7" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3855,29 +3919,32 @@
       <c r="E1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
+      <c r="F1" s="8" t="s">
+        <v>486</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>0</v>
       </c>
@@ -3900,20 +3967,23 @@
         <v>1</v>
       </c>
       <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
         <v>1.5</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2">
         <v>1</v>
       </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
       <c r="K2" s="2">
         <v>0</v>
       </c>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>0</v>
       </c>
@@ -3936,20 +4006,23 @@
         <v>2</v>
       </c>
       <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2">
         <v>3</v>
       </c>
-      <c r="I3" s="2">
-        <v>2</v>
-      </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2">
         <v>0</v>
       </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>0</v>
       </c>
@@ -3972,20 +4045,23 @@
         <v>0.5</v>
       </c>
       <c r="H4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="2">
         <v>1</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>0.5</v>
       </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
       <c r="K4" s="2">
         <v>0</v>
       </c>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>0</v>
       </c>
@@ -4008,20 +4084,23 @@
         <v>2</v>
       </c>
       <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2">
         <v>3</v>
       </c>
-      <c r="I5" s="2">
-        <v>2</v>
-      </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
       </c>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>0</v>
       </c>
@@ -4044,20 +4123,23 @@
         <v>0.5</v>
       </c>
       <c r="H6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <v>0.5</v>
       </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
       <c r="K6" s="2">
         <v>0</v>
       </c>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>0</v>
       </c>
@@ -4080,20 +4162,23 @@
         <v>1</v>
       </c>
       <c r="H7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
         <v>1</v>
       </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
       <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>0</v>
       </c>
@@ -4116,20 +4201,23 @@
         <v>1</v>
       </c>
       <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>1.5</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <v>1</v>
       </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
       <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>0</v>
       </c>
@@ -4152,20 +4240,23 @@
         <v>2.5</v>
       </c>
       <c r="H9" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="2">
         <v>4</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2">
         <v>2.5</v>
       </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
       <c r="K9" s="2">
         <v>0</v>
       </c>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>0</v>
       </c>
@@ -4188,20 +4279,23 @@
         <v>3.5</v>
       </c>
       <c r="H10" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="I10" s="2">
         <v>6</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <v>3.5</v>
       </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
       <c r="K10" s="2">
         <v>0</v>
       </c>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>0</v>
       </c>
@@ -4224,20 +4318,23 @@
         <v>1</v>
       </c>
       <c r="H11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
         <v>1</v>
       </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
       <c r="K11" s="2">
         <v>0</v>
       </c>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>0</v>
       </c>
@@ -4260,20 +4357,23 @@
         <v>2.5</v>
       </c>
       <c r="H12" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I12" s="2">
         <v>4</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <v>2.5</v>
       </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
       <c r="K12" s="2">
         <v>0</v>
       </c>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>0</v>
       </c>
@@ -4296,22 +4396,25 @@
         <v>1</v>
       </c>
       <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
         <v>1.4</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="2">
         <v>0.7</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <v>0.6</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <v>0.3</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>0</v>
       </c>
@@ -4334,20 +4437,23 @@
         <v>1</v>
       </c>
       <c r="H14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2">
         <v>1</v>
       </c>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>0</v>
       </c>
@@ -4370,20 +4476,23 @@
         <v>2</v>
       </c>
       <c r="H15" s="2">
+        <v>2</v>
+      </c>
+      <c r="I15" s="2">
         <v>3</v>
       </c>
-      <c r="I15" s="2">
-        <v>2</v>
-      </c>
       <c r="J15" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
       </c>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>0</v>
       </c>
@@ -4406,20 +4515,23 @@
         <v>1</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
         <v>1</v>
       </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
       <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>0</v>
       </c>
@@ -4442,20 +4554,23 @@
         <v>1.5</v>
       </c>
       <c r="H17" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I17" s="2">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
         <v>1.5</v>
       </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
       <c r="K17" s="2">
         <v>0</v>
       </c>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>0</v>
       </c>
@@ -4478,20 +4593,23 @@
         <v>1.5</v>
       </c>
       <c r="H18" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I18" s="2">
+        <v>2</v>
+      </c>
+      <c r="J18" s="2">
         <v>1.5</v>
       </c>
-      <c r="J18" s="2">
-        <v>0</v>
-      </c>
       <c r="K18" s="2">
         <v>0</v>
       </c>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>0</v>
       </c>
@@ -4514,20 +4632,23 @@
         <v>2.5</v>
       </c>
       <c r="H19" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
       </c>
       <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
         <v>3</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <v>2.5</v>
       </c>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>0</v>
       </c>
@@ -4550,20 +4671,23 @@
         <v>1</v>
       </c>
       <c r="H20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
       </c>
       <c r="J20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2">
         <v>1</v>
       </c>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L20" s="2">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>10</v>
       </c>
@@ -4586,20 +4710,23 @@
         <v>1</v>
       </c>
       <c r="H21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2">
         <v>1</v>
       </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
       <c r="K21" s="2">
         <v>0</v>
       </c>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>10</v>
       </c>
@@ -4622,20 +4749,23 @@
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2">
         <v>1</v>
       </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
       <c r="K22" s="2">
         <v>0</v>
       </c>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>10</v>
       </c>
@@ -4658,20 +4788,23 @@
         <v>0.8</v>
       </c>
       <c r="H23" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I23" s="2">
         <v>1.5</v>
       </c>
-      <c r="I23" s="2">
+      <c r="J23" s="2">
         <v>0.8</v>
       </c>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
       <c r="K23" s="2">
         <v>0</v>
       </c>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>10</v>
       </c>
@@ -4694,20 +4827,23 @@
         <v>0.8</v>
       </c>
       <c r="H24" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I24" s="2">
         <v>1.5</v>
       </c>
-      <c r="I24" s="2">
+      <c r="J24" s="2">
         <v>0.8</v>
       </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
       <c r="K24" s="2">
         <v>0</v>
       </c>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>10</v>
       </c>
@@ -4730,20 +4866,23 @@
         <v>1.5</v>
       </c>
       <c r="H25" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I25" s="2">
         <v>3</v>
       </c>
-      <c r="I25" s="2">
+      <c r="J25" s="2">
         <v>1.5</v>
       </c>
-      <c r="J25" s="2">
-        <v>0</v>
-      </c>
       <c r="K25" s="2">
         <v>0</v>
       </c>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>10</v>
       </c>
@@ -4766,20 +4905,23 @@
         <v>0.8</v>
       </c>
       <c r="H26" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I26" s="2">
         <v>1.5</v>
       </c>
-      <c r="I26" s="2">
+      <c r="J26" s="2">
         <v>0.8</v>
       </c>
-      <c r="J26" s="2">
-        <v>0</v>
-      </c>
       <c r="K26" s="2">
         <v>0</v>
       </c>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>10</v>
       </c>
@@ -4802,20 +4944,23 @@
         <v>1.2</v>
       </c>
       <c r="H27" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="I27" s="2">
         <v>2.5</v>
       </c>
-      <c r="I27" s="2">
+      <c r="J27" s="2">
         <v>1.2</v>
       </c>
-      <c r="J27" s="2">
-        <v>0</v>
-      </c>
       <c r="K27" s="2">
         <v>0</v>
       </c>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>10</v>
       </c>
@@ -4838,20 +4983,23 @@
         <v>1.5</v>
       </c>
       <c r="H28" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I28" s="2">
         <v>3</v>
       </c>
-      <c r="I28" s="2">
+      <c r="J28" s="2">
         <v>1.5</v>
       </c>
-      <c r="J28" s="2">
-        <v>0</v>
-      </c>
       <c r="K28" s="2">
         <v>0</v>
       </c>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>10</v>
       </c>
@@ -4874,20 +5022,23 @@
         <v>4</v>
       </c>
       <c r="H29" s="2">
+        <v>4</v>
+      </c>
+      <c r="I29" s="2">
         <v>8</v>
       </c>
-      <c r="I29" s="2">
+      <c r="J29" s="2">
         <v>4</v>
       </c>
-      <c r="J29" s="2">
-        <v>0</v>
-      </c>
       <c r="K29" s="2">
         <v>0</v>
       </c>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>10</v>
       </c>
@@ -4910,20 +5061,23 @@
         <v>2</v>
       </c>
       <c r="H30" s="2">
+        <v>2</v>
+      </c>
+      <c r="I30" s="2">
         <v>4</v>
       </c>
-      <c r="I30" s="2">
-        <v>2</v>
-      </c>
       <c r="J30" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" s="2">
         <v>0</v>
       </c>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>10</v>
       </c>
@@ -4946,20 +5100,23 @@
         <v>2.5</v>
       </c>
       <c r="H31" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I31" s="2">
         <v>5</v>
       </c>
-      <c r="I31" s="2">
+      <c r="J31" s="2">
         <v>2.5</v>
       </c>
-      <c r="J31" s="2">
-        <v>0</v>
-      </c>
       <c r="K31" s="2">
         <v>0</v>
       </c>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>10</v>
       </c>
@@ -4982,20 +5139,23 @@
         <v>2</v>
       </c>
       <c r="H32" s="2">
+        <v>2</v>
+      </c>
+      <c r="I32" s="2">
         <v>3</v>
       </c>
-      <c r="I32" s="2">
-        <v>2</v>
-      </c>
       <c r="J32" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" s="2">
         <v>0</v>
       </c>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>10</v>
       </c>
@@ -5018,20 +5178,23 @@
         <v>1.5</v>
       </c>
       <c r="H33" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I33" s="2">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
         <v>1.5</v>
       </c>
-      <c r="J33" s="2">
-        <v>0</v>
-      </c>
       <c r="K33" s="2">
         <v>0</v>
       </c>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>10</v>
       </c>
@@ -5054,20 +5217,23 @@
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
       </c>
       <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
         <v>4</v>
       </c>
-      <c r="K34" s="2">
+      <c r="L34" s="2">
         <v>3</v>
       </c>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>10</v>
       </c>
@@ -5090,20 +5256,23 @@
         <v>1</v>
       </c>
       <c r="H35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
       </c>
       <c r="J35" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35" s="2">
+        <v>2</v>
+      </c>
+      <c r="L35" s="2">
         <v>1</v>
       </c>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>10</v>
       </c>
@@ -5126,20 +5295,23 @@
         <v>3</v>
       </c>
       <c r="H36" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" s="2">
         <v>0</v>
       </c>
       <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2">
         <v>5</v>
       </c>
-      <c r="K36" s="2">
+      <c r="L36" s="2">
         <v>3</v>
       </c>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>10</v>
       </c>
@@ -5162,20 +5334,23 @@
         <v>1</v>
       </c>
       <c r="H37" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="2">
+        <v>2</v>
+      </c>
+      <c r="J37" s="2">
         <v>1</v>
       </c>
-      <c r="J37" s="2">
-        <v>0</v>
-      </c>
       <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>10</v>
       </c>
@@ -5198,20 +5373,23 @@
         <v>2.5</v>
       </c>
       <c r="H38" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I38" s="2">
         <v>4</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>2.5</v>
       </c>
-      <c r="J38" s="2">
-        <v>0</v>
-      </c>
       <c r="K38" s="2">
         <v>0</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>10</v>
       </c>
@@ -5234,20 +5412,23 @@
         <v>3.5</v>
       </c>
       <c r="H39" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="I39" s="2">
         <v>6</v>
       </c>
-      <c r="I39" s="2">
+      <c r="J39" s="2">
         <v>3.5</v>
       </c>
-      <c r="J39" s="2">
-        <v>0</v>
-      </c>
       <c r="K39" s="2">
         <v>0</v>
       </c>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>10</v>
       </c>
@@ -5270,20 +5451,23 @@
         <v>2</v>
       </c>
       <c r="H40" s="2">
+        <v>2</v>
+      </c>
+      <c r="I40" s="2">
         <v>4</v>
       </c>
-      <c r="I40" s="2">
-        <v>2</v>
-      </c>
       <c r="J40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2">
         <v>0</v>
       </c>
-      <c r="L40" s="2"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>10</v>
       </c>
@@ -5306,20 +5490,23 @@
         <v>1.2</v>
       </c>
       <c r="H41" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="I41" s="2">
         <v>2.5</v>
       </c>
-      <c r="I41" s="2">
+      <c r="J41" s="2">
         <v>1.2</v>
       </c>
-      <c r="J41" s="2">
-        <v>0</v>
-      </c>
       <c r="K41" s="2">
         <v>0</v>
       </c>
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L41" s="2">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>10</v>
       </c>
@@ -5342,20 +5529,23 @@
         <v>2</v>
       </c>
       <c r="H42" s="2">
+        <v>2</v>
+      </c>
+      <c r="I42" s="2">
         <v>4</v>
       </c>
-      <c r="I42" s="2">
-        <v>2</v>
-      </c>
       <c r="J42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2">
         <v>0</v>
       </c>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L42" s="2">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>10</v>
       </c>
@@ -5378,20 +5568,23 @@
         <v>1.2</v>
       </c>
       <c r="H43" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="I43" s="2">
         <v>2.5</v>
       </c>
-      <c r="I43" s="2">
+      <c r="J43" s="2">
         <v>1.2</v>
       </c>
-      <c r="J43" s="2">
-        <v>0</v>
-      </c>
       <c r="K43" s="2">
         <v>0</v>
       </c>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L43" s="2">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>10</v>
       </c>
@@ -5414,20 +5607,23 @@
         <v>1</v>
       </c>
       <c r="H44" s="2">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2">
         <v>1.5</v>
       </c>
-      <c r="I44" s="2">
+      <c r="J44" s="2">
         <v>1</v>
       </c>
-      <c r="J44" s="2">
-        <v>0</v>
-      </c>
       <c r="K44" s="2">
         <v>0</v>
       </c>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L44" s="2">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>10</v>
       </c>
@@ -5450,20 +5646,23 @@
         <v>0.8</v>
       </c>
       <c r="H45" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I45" s="2">
         <v>1.5</v>
       </c>
-      <c r="I45" s="2">
+      <c r="J45" s="2">
         <v>0.8</v>
       </c>
-      <c r="J45" s="2">
-        <v>0</v>
-      </c>
       <c r="K45" s="2">
         <v>0</v>
       </c>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L45" s="2">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>10</v>
       </c>
@@ -5486,20 +5685,23 @@
         <v>0.8</v>
       </c>
       <c r="H46" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I46" s="2">
         <v>1.5</v>
       </c>
-      <c r="I46" s="2">
+      <c r="J46" s="2">
         <v>0.8</v>
       </c>
-      <c r="J46" s="2">
-        <v>0</v>
-      </c>
       <c r="K46" s="2">
         <v>0</v>
       </c>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L46" s="2">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>10</v>
       </c>
@@ -5522,20 +5724,23 @@
         <v>1</v>
       </c>
       <c r="H47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="2">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2">
         <v>1</v>
       </c>
-      <c r="J47" s="2">
-        <v>0</v>
-      </c>
       <c r="K47" s="2">
         <v>0</v>
       </c>
-      <c r="L47" s="2"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L47" s="2">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>10</v>
       </c>
@@ -5558,20 +5763,23 @@
         <v>0.8</v>
       </c>
       <c r="H48" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I48" s="2">
         <v>1</v>
       </c>
-      <c r="I48" s="2">
+      <c r="J48" s="2">
         <v>0.8</v>
       </c>
-      <c r="J48" s="2">
-        <v>0</v>
-      </c>
       <c r="K48" s="2">
         <v>0</v>
       </c>
-      <c r="L48" s="2"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L48" s="2">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>10</v>
       </c>
@@ -5594,22 +5802,25 @@
         <v>2.5</v>
       </c>
       <c r="H49" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2">
         <v>2.5</v>
       </c>
-      <c r="J49" s="2">
-        <v>0</v>
-      </c>
       <c r="K49" s="2">
         <v>0</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="L49" s="2">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>10</v>
       </c>
@@ -5632,22 +5843,25 @@
         <v>2.5</v>
       </c>
       <c r="H50" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2">
         <v>2.5</v>
       </c>
-      <c r="J50" s="2">
-        <v>0</v>
-      </c>
       <c r="K50" s="2">
         <v>0</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="2">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>10</v>
       </c>
@@ -5670,20 +5884,23 @@
         <v>1</v>
       </c>
       <c r="H51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="2">
+        <v>2</v>
+      </c>
+      <c r="J51" s="2">
         <v>1</v>
       </c>
-      <c r="J51" s="2">
-        <v>0</v>
-      </c>
       <c r="K51" s="2">
         <v>0</v>
       </c>
-      <c r="L51" s="2"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L51" s="2">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>10</v>
       </c>
@@ -5706,22 +5923,25 @@
         <v>5</v>
       </c>
       <c r="H52" s="2">
+        <v>5</v>
+      </c>
+      <c r="I52" s="2">
         <v>12</v>
       </c>
-      <c r="I52" s="2">
+      <c r="J52" s="2">
         <v>5</v>
       </c>
-      <c r="J52" s="2">
-        <v>0</v>
-      </c>
       <c r="K52" s="2">
         <v>0</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>10</v>
       </c>
@@ -5744,20 +5964,23 @@
         <v>3</v>
       </c>
       <c r="H53" s="2">
+        <v>3</v>
+      </c>
+      <c r="I53" s="2">
         <v>5</v>
       </c>
-      <c r="I53" s="2">
+      <c r="J53" s="2">
         <v>3</v>
       </c>
-      <c r="J53" s="2">
-        <v>0</v>
-      </c>
       <c r="K53" s="2">
         <v>0</v>
       </c>
-      <c r="L53" s="2"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L53" s="2">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>10</v>
       </c>
@@ -5780,20 +6003,23 @@
         <v>2.5</v>
       </c>
       <c r="H54" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I54" s="2">
         <v>4</v>
       </c>
-      <c r="I54" s="2">
+      <c r="J54" s="2">
         <v>2.5</v>
       </c>
-      <c r="J54" s="2">
-        <v>0</v>
-      </c>
       <c r="K54" s="2">
         <v>0</v>
       </c>
-      <c r="L54" s="2"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L54" s="2">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>10</v>
       </c>
@@ -5816,20 +6042,23 @@
         <v>1.5</v>
       </c>
       <c r="H55" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I55" s="2">
+        <v>2</v>
+      </c>
+      <c r="J55" s="2">
         <v>1.5</v>
       </c>
-      <c r="J55" s="2">
-        <v>0</v>
-      </c>
       <c r="K55" s="2">
         <v>0</v>
       </c>
-      <c r="L55" s="2"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L55" s="2">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>10</v>
       </c>
@@ -5852,20 +6081,23 @@
         <v>2</v>
       </c>
       <c r="H56" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I56" s="2">
         <v>0</v>
       </c>
       <c r="J56" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K56" s="2">
         <v>2</v>
       </c>
-      <c r="L56" s="2"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L56" s="2">
+        <v>2</v>
+      </c>
+      <c r="M56" s="2"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>10</v>
       </c>
@@ -5888,20 +6120,23 @@
         <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="2">
+        <v>2</v>
+      </c>
+      <c r="J57" s="2">
         <v>1</v>
       </c>
-      <c r="J57" s="2">
-        <v>0</v>
-      </c>
       <c r="K57" s="2">
         <v>0</v>
       </c>
-      <c r="L57" s="2"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L57" s="2">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>10</v>
       </c>
@@ -5924,20 +6159,23 @@
         <v>2.5</v>
       </c>
       <c r="H58" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I58" s="2">
         <v>4</v>
       </c>
-      <c r="I58" s="2">
+      <c r="J58" s="2">
         <v>2.5</v>
       </c>
-      <c r="J58" s="2">
-        <v>0</v>
-      </c>
       <c r="K58" s="2">
         <v>0</v>
       </c>
-      <c r="L58" s="2"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L58" s="2">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>10</v>
       </c>
@@ -5960,22 +6198,25 @@
         <v>6</v>
       </c>
       <c r="H59" s="2">
+        <v>6</v>
+      </c>
+      <c r="I59" s="2">
         <v>12</v>
       </c>
-      <c r="I59" s="2">
+      <c r="J59" s="2">
         <v>6</v>
       </c>
-      <c r="J59" s="2">
-        <v>0</v>
-      </c>
       <c r="K59" s="2">
         <v>0</v>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="L59" s="2">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>10</v>
       </c>
@@ -5998,22 +6239,25 @@
         <v>2</v>
       </c>
       <c r="H60" s="2">
+        <v>2</v>
+      </c>
+      <c r="I60" s="2">
         <v>1.8</v>
-      </c>
-      <c r="I60" s="2">
-        <v>1.2</v>
       </c>
       <c r="J60" s="2">
         <v>1.2</v>
       </c>
       <c r="K60" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="L60" s="2">
         <v>0.8</v>
       </c>
-      <c r="L60" s="2" t="s">
+      <c r="M60" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>10</v>
       </c>
@@ -6036,20 +6280,23 @@
         <v>0.5</v>
       </c>
       <c r="H61" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I61" s="2">
         <v>1</v>
       </c>
-      <c r="I61" s="2">
+      <c r="J61" s="2">
         <v>0.5</v>
       </c>
-      <c r="J61" s="2">
-        <v>0</v>
-      </c>
       <c r="K61" s="2">
         <v>0</v>
       </c>
-      <c r="L61" s="2"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L61" s="2">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>10</v>
       </c>
@@ -6072,20 +6319,23 @@
         <v>1.5</v>
       </c>
       <c r="H62" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I62" s="2">
         <v>3</v>
       </c>
-      <c r="I62" s="2">
+      <c r="J62" s="2">
         <v>1.5</v>
       </c>
-      <c r="J62" s="2">
-        <v>0</v>
-      </c>
       <c r="K62" s="2">
         <v>0</v>
       </c>
-      <c r="L62" s="2"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L62" s="2">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>10</v>
       </c>
@@ -6108,22 +6358,25 @@
         <v>1</v>
       </c>
       <c r="H63" s="2">
+        <v>1</v>
+      </c>
+      <c r="I63" s="2">
         <v>0.45</v>
       </c>
-      <c r="I63" s="2">
+      <c r="J63" s="2">
         <v>0.3</v>
       </c>
-      <c r="J63" s="2">
+      <c r="K63" s="2">
         <v>1.05</v>
       </c>
-      <c r="K63" s="2">
+      <c r="L63" s="2">
         <v>0.7</v>
       </c>
-      <c r="L63" s="2" t="s">
+      <c r="M63" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>10</v>
       </c>
@@ -6146,20 +6399,23 @@
         <v>1.5</v>
       </c>
       <c r="H64" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I64" s="2">
+        <v>2</v>
+      </c>
+      <c r="J64" s="2">
         <v>1.5</v>
       </c>
-      <c r="J64" s="2">
-        <v>0</v>
-      </c>
       <c r="K64" s="2">
         <v>0</v>
       </c>
-      <c r="L64" s="2"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L64" s="2">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>10</v>
       </c>
@@ -6182,20 +6438,23 @@
         <v>2</v>
       </c>
       <c r="H65" s="2">
+        <v>2</v>
+      </c>
+      <c r="I65" s="2">
         <v>3</v>
       </c>
-      <c r="I65" s="2">
-        <v>2</v>
-      </c>
       <c r="J65" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K65" s="2">
         <v>0</v>
       </c>
-      <c r="L65" s="2"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L65" s="2">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>10</v>
       </c>
@@ -6218,20 +6477,23 @@
         <v>1.5</v>
       </c>
       <c r="H66" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I66" s="2">
         <v>1.4</v>
       </c>
-      <c r="I66" s="2">
+      <c r="J66" s="2">
         <v>1.05</v>
       </c>
-      <c r="J66" s="2">
+      <c r="K66" s="2">
         <v>0.6</v>
       </c>
-      <c r="K66" s="2">
+      <c r="L66" s="2">
         <v>0.45</v>
       </c>
-      <c r="L66" s="2"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M66" s="2"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>10</v>
       </c>
@@ -6254,20 +6516,23 @@
         <v>2</v>
       </c>
       <c r="H67" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67" s="2">
         <v>0</v>
       </c>
       <c r="J67" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" s="2">
         <v>2</v>
       </c>
-      <c r="L67" s="2"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L67" s="2">
+        <v>2</v>
+      </c>
+      <c r="M67" s="2"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>10</v>
       </c>
@@ -6290,20 +6555,23 @@
         <v>3.5</v>
       </c>
       <c r="H68" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I68" s="2">
         <v>0</v>
       </c>
       <c r="J68" s="2">
+        <v>0</v>
+      </c>
+      <c r="K68" s="2">
         <v>4</v>
       </c>
-      <c r="K68" s="2">
+      <c r="L68" s="2">
         <v>3.5</v>
       </c>
-      <c r="L68" s="2"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M68" s="2"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>11</v>
       </c>
@@ -6326,20 +6594,23 @@
         <v>1</v>
       </c>
       <c r="H69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="2">
         <v>0</v>
       </c>
       <c r="J69" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K69" s="2">
+        <v>2</v>
+      </c>
+      <c r="L69" s="2">
         <v>1</v>
       </c>
-      <c r="L69" s="2"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M69" s="2"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>11</v>
       </c>
@@ -6362,20 +6633,23 @@
         <v>1.5</v>
       </c>
       <c r="H70" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I70" s="2">
         <v>0</v>
       </c>
       <c r="J70" s="2">
+        <v>0</v>
+      </c>
+      <c r="K70" s="2">
         <v>3</v>
       </c>
-      <c r="K70" s="2">
+      <c r="L70" s="2">
         <v>1.5</v>
       </c>
-      <c r="L70" s="2"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M70" s="2"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>11</v>
       </c>
@@ -6398,22 +6672,25 @@
         <v>1</v>
       </c>
       <c r="H71" s="2">
+        <v>1</v>
+      </c>
+      <c r="I71" s="2">
         <v>0.8</v>
       </c>
-      <c r="I71" s="2">
+      <c r="J71" s="2">
         <v>0.4</v>
       </c>
-      <c r="J71" s="2">
+      <c r="K71" s="2">
         <v>1.2</v>
       </c>
-      <c r="K71" s="2">
+      <c r="L71" s="2">
         <v>0.6</v>
       </c>
-      <c r="L71" s="2" t="s">
+      <c r="M71" s="2" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>11</v>
       </c>
@@ -6436,22 +6713,25 @@
         <v>16.5</v>
       </c>
       <c r="H72" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="I72" s="2">
         <v>18</v>
       </c>
-      <c r="I72" s="2">
+      <c r="J72" s="2">
         <v>5.5</v>
       </c>
-      <c r="J72" s="2">
+      <c r="K72" s="2">
         <v>36</v>
       </c>
-      <c r="K72" s="2">
+      <c r="L72" s="2">
         <v>11</v>
       </c>
-      <c r="L72" s="2" t="s">
+      <c r="M72" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>11</v>
       </c>
@@ -6474,20 +6754,23 @@
         <v>8.5</v>
       </c>
       <c r="H73" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I73" s="2">
         <v>0</v>
       </c>
       <c r="J73" s="2">
+        <v>0</v>
+      </c>
+      <c r="K73" s="2">
         <v>28</v>
       </c>
-      <c r="K73" s="2">
+      <c r="L73" s="2">
         <v>8.5</v>
       </c>
-      <c r="L73" s="2"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M73" s="2"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>11</v>
       </c>
@@ -6510,22 +6793,25 @@
         <v>12.5</v>
       </c>
       <c r="H74" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="I74" s="2">
         <v>5</v>
       </c>
-      <c r="I74" s="2">
+      <c r="J74" s="2">
         <v>1.5</v>
       </c>
-      <c r="J74" s="2">
+      <c r="K74" s="2">
         <v>36</v>
       </c>
-      <c r="K74" s="2">
+      <c r="L74" s="2">
         <v>11</v>
       </c>
-      <c r="L74" s="2" t="s">
+      <c r="M74" s="2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>11</v>
       </c>
@@ -6548,20 +6834,23 @@
         <v>8.5</v>
       </c>
       <c r="H75" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I75" s="2">
         <v>0</v>
       </c>
       <c r="J75" s="2">
+        <v>0</v>
+      </c>
+      <c r="K75" s="2">
         <v>28</v>
       </c>
-      <c r="K75" s="2">
+      <c r="L75" s="2">
         <v>8.5</v>
       </c>
-      <c r="L75" s="2"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M75" s="2"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>11</v>
       </c>
@@ -6584,20 +6873,23 @@
         <v>8.5</v>
       </c>
       <c r="H76" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I76" s="2">
         <v>0</v>
       </c>
       <c r="J76" s="2">
+        <v>0</v>
+      </c>
+      <c r="K76" s="2">
         <v>28</v>
       </c>
-      <c r="K76" s="2">
+      <c r="L76" s="2">
         <v>8.5</v>
       </c>
-      <c r="L76" s="2"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M76" s="2"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>11</v>
       </c>
@@ -6620,20 +6912,23 @@
         <v>33</v>
       </c>
       <c r="H77" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I77" s="2">
         <v>0</v>
       </c>
       <c r="J77" s="2">
+        <v>0</v>
+      </c>
+      <c r="K77" s="2">
         <v>114</v>
       </c>
-      <c r="K77" s="2">
+      <c r="L77" s="2">
         <v>33</v>
       </c>
-      <c r="L77" s="2"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M77" s="2"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>11</v>
       </c>
@@ -6656,22 +6951,25 @@
         <v>12</v>
       </c>
       <c r="H78" s="2">
+        <v>12</v>
+      </c>
+      <c r="I78" s="2">
         <v>4</v>
       </c>
-      <c r="I78" s="2">
+      <c r="J78" s="2">
         <v>5</v>
       </c>
-      <c r="J78" s="2">
+      <c r="K78" s="2">
         <v>11</v>
       </c>
-      <c r="K78" s="2">
+      <c r="L78" s="2">
         <v>7</v>
       </c>
-      <c r="L78" s="2" t="s">
+      <c r="M78" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>11</v>
       </c>
@@ -6694,20 +6992,23 @@
         <v>6</v>
       </c>
       <c r="H79" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I79" s="2">
         <v>0</v>
       </c>
       <c r="J79" s="2">
+        <v>0</v>
+      </c>
+      <c r="K79" s="2">
         <v>10</v>
       </c>
-      <c r="K79" s="2">
+      <c r="L79" s="2">
         <v>6</v>
       </c>
-      <c r="L79" s="2"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M79" s="2"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>11</v>
       </c>
@@ -6730,20 +7031,23 @@
         <v>7</v>
       </c>
       <c r="H80" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I80" s="2">
         <v>0</v>
       </c>
       <c r="J80" s="2">
+        <v>0</v>
+      </c>
+      <c r="K80" s="2">
         <v>12</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>7</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>11</v>
       </c>
@@ -6766,20 +7070,23 @@
         <v>5</v>
       </c>
       <c r="H81" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I81" s="2">
         <v>0</v>
       </c>
       <c r="J81" s="2">
+        <v>0</v>
+      </c>
+      <c r="K81" s="2">
         <v>8</v>
       </c>
-      <c r="K81" s="2">
+      <c r="L81" s="2">
         <v>5</v>
       </c>
-      <c r="L81" s="2"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M81" s="2"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>11</v>
       </c>
@@ -6802,20 +7109,23 @@
         <v>5</v>
       </c>
       <c r="H82" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I82" s="2">
         <v>0</v>
       </c>
       <c r="J82" s="2">
+        <v>0</v>
+      </c>
+      <c r="K82" s="2">
         <v>8</v>
       </c>
-      <c r="K82" s="2">
+      <c r="L82" s="2">
         <v>5</v>
       </c>
-      <c r="L82" s="2"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M82" s="2"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>11</v>
       </c>
@@ -6838,20 +7148,23 @@
         <v>6</v>
       </c>
       <c r="H83" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I83" s="2">
         <v>0</v>
       </c>
       <c r="J83" s="2">
+        <v>0</v>
+      </c>
+      <c r="K83" s="2">
         <v>10</v>
       </c>
-      <c r="K83" s="2">
+      <c r="L83" s="2">
         <v>6</v>
       </c>
-      <c r="L83" s="2"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M83" s="2"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>11</v>
       </c>
@@ -6874,20 +7187,23 @@
         <v>5</v>
       </c>
       <c r="H84" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I84" s="2">
         <v>0</v>
       </c>
       <c r="J84" s="2">
+        <v>0</v>
+      </c>
+      <c r="K84" s="2">
         <v>6</v>
       </c>
-      <c r="K84" s="2">
+      <c r="L84" s="2">
         <v>5</v>
       </c>
-      <c r="L84" s="2"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M84" s="2"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>11</v>
       </c>
@@ -6910,20 +7226,23 @@
         <v>3.5</v>
       </c>
       <c r="H85" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I85" s="2">
         <v>0</v>
       </c>
       <c r="J85" s="2">
+        <v>0</v>
+      </c>
+      <c r="K85" s="2">
         <v>4</v>
       </c>
-      <c r="K85" s="2">
+      <c r="L85" s="2">
         <v>3.5</v>
       </c>
-      <c r="L85" s="2"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M85" s="2"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>12</v>
       </c>
@@ -6946,20 +7265,23 @@
         <v>3</v>
       </c>
       <c r="H86" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I86" s="2">
         <v>0</v>
       </c>
       <c r="J86" s="2">
+        <v>0</v>
+      </c>
+      <c r="K86" s="2">
         <v>5</v>
       </c>
-      <c r="K86" s="2">
+      <c r="L86" s="2">
         <v>3</v>
       </c>
-      <c r="L86" s="2"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M86" s="2"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>12</v>
       </c>
@@ -6982,20 +7304,23 @@
         <v>2</v>
       </c>
       <c r="H87" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I87" s="2">
         <v>0</v>
       </c>
       <c r="J87" s="2">
+        <v>0</v>
+      </c>
+      <c r="K87" s="2">
         <v>4</v>
       </c>
-      <c r="K87" s="2">
-        <v>2</v>
-      </c>
-      <c r="L87" s="2"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L87" s="2">
+        <v>2</v>
+      </c>
+      <c r="M87" s="2"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>12</v>
       </c>
@@ -7018,20 +7343,23 @@
         <v>2.5</v>
       </c>
       <c r="H88" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I88" s="2">
         <v>0</v>
       </c>
       <c r="J88" s="2">
+        <v>0</v>
+      </c>
+      <c r="K88" s="2">
         <v>5</v>
       </c>
-      <c r="K88" s="2">
+      <c r="L88" s="2">
         <v>2.5</v>
       </c>
-      <c r="L88" s="2"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M88" s="2"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>12</v>
       </c>
@@ -7054,22 +7382,25 @@
         <v>16</v>
       </c>
       <c r="H89" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I89" s="2">
         <v>0</v>
       </c>
       <c r="J89" s="2">
+        <v>0</v>
+      </c>
+      <c r="K89" s="2">
         <v>40</v>
       </c>
-      <c r="K89" s="2">
+      <c r="L89" s="2">
         <v>16</v>
       </c>
-      <c r="L89" s="2" t="s">
+      <c r="M89" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>12</v>
       </c>
@@ -7092,20 +7423,23 @@
         <v>2.5</v>
       </c>
       <c r="H90" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I90" s="2">
         <v>0</v>
       </c>
       <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2">
         <v>4</v>
       </c>
-      <c r="K90" s="2">
+      <c r="L90" s="2">
         <v>2.5</v>
       </c>
-      <c r="L90" s="2"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M90" s="2"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>12</v>
       </c>
@@ -7128,20 +7462,23 @@
         <v>2.5</v>
       </c>
       <c r="H91" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I91" s="2">
         <v>0</v>
       </c>
       <c r="J91" s="2">
+        <v>0</v>
+      </c>
+      <c r="K91" s="2">
         <v>3</v>
       </c>
-      <c r="K91" s="2">
+      <c r="L91" s="2">
         <v>2.5</v>
       </c>
-      <c r="L91" s="2"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M91" s="2"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>13</v>
       </c>
@@ -7164,20 +7501,23 @@
         <v>3</v>
       </c>
       <c r="H92" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I92" s="2">
         <v>0</v>
       </c>
       <c r="J92" s="2">
+        <v>0</v>
+      </c>
+      <c r="K92" s="2">
         <v>5</v>
       </c>
-      <c r="K92" s="2">
+      <c r="L92" s="2">
         <v>3</v>
       </c>
-      <c r="L92" s="2"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M92" s="2"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>13</v>
       </c>
@@ -7200,20 +7540,23 @@
         <v>4</v>
       </c>
       <c r="H93" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I93" s="2">
         <v>0</v>
       </c>
       <c r="J93" s="2">
+        <v>0</v>
+      </c>
+      <c r="K93" s="2">
         <v>8</v>
       </c>
-      <c r="K93" s="2">
+      <c r="L93" s="2">
         <v>4</v>
       </c>
-      <c r="L93" s="2"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M93" s="2"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>13</v>
       </c>
@@ -7236,20 +7579,23 @@
         <v>4</v>
       </c>
       <c r="H94" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I94" s="2">
         <v>0</v>
       </c>
       <c r="J94" s="2">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2">
         <v>8</v>
       </c>
-      <c r="K94" s="2">
+      <c r="L94" s="2">
         <v>4</v>
       </c>
-      <c r="L94" s="2"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M94" s="2"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>13</v>
       </c>
@@ -7272,20 +7618,23 @@
         <v>3</v>
       </c>
       <c r="H95" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I95" s="2">
         <v>0</v>
       </c>
       <c r="J95" s="2">
+        <v>0</v>
+      </c>
+      <c r="K95" s="2">
         <v>6</v>
       </c>
-      <c r="K95" s="2">
+      <c r="L95" s="2">
         <v>3</v>
       </c>
-      <c r="L95" s="2"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M95" s="2"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>13</v>
       </c>
@@ -7308,20 +7657,23 @@
         <v>1.5</v>
       </c>
       <c r="H96" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I96" s="2">
         <v>0</v>
       </c>
       <c r="J96" s="2">
+        <v>0</v>
+      </c>
+      <c r="K96" s="2">
         <v>3</v>
       </c>
-      <c r="K96" s="2">
+      <c r="L96" s="2">
         <v>1.5</v>
       </c>
-      <c r="L96" s="2"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M96" s="2"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>13</v>
       </c>
@@ -7344,20 +7696,23 @@
         <v>2</v>
       </c>
       <c r="H97" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I97" s="2">
         <v>0</v>
       </c>
       <c r="J97" s="2">
+        <v>0</v>
+      </c>
+      <c r="K97" s="2">
         <v>3</v>
       </c>
-      <c r="K97" s="2">
-        <v>2</v>
-      </c>
-      <c r="L97" s="2"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L97" s="2">
+        <v>2</v>
+      </c>
+      <c r="M97" s="2"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>13</v>
       </c>
@@ -7380,20 +7735,23 @@
         <v>2</v>
       </c>
       <c r="H98" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I98" s="2">
         <v>0</v>
       </c>
       <c r="J98" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K98" s="2">
         <v>2</v>
       </c>
-      <c r="L98" s="2"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L98" s="2">
+        <v>2</v>
+      </c>
+      <c r="M98" s="2"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>14</v>
       </c>
@@ -7416,20 +7774,23 @@
         <v>2.5</v>
       </c>
       <c r="H99" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I99" s="2">
         <v>0</v>
       </c>
       <c r="J99" s="2">
+        <v>0</v>
+      </c>
+      <c r="K99" s="2">
         <v>4</v>
       </c>
-      <c r="K99" s="2">
+      <c r="L99" s="2">
         <v>2.5</v>
       </c>
-      <c r="L99" s="2"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M99" s="2"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>14</v>
       </c>
@@ -7452,20 +7813,23 @@
         <v>6</v>
       </c>
       <c r="H100" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I100" s="2">
         <v>0</v>
       </c>
       <c r="J100" s="2">
+        <v>0</v>
+      </c>
+      <c r="K100" s="2">
         <v>12</v>
       </c>
-      <c r="K100" s="2">
+      <c r="L100" s="2">
         <v>6</v>
       </c>
-      <c r="L100" s="2"/>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M100" s="2"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>14</v>
       </c>
@@ -7488,20 +7852,23 @@
         <v>3</v>
       </c>
       <c r="H101" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I101" s="2">
         <v>0</v>
       </c>
       <c r="J101" s="2">
+        <v>0</v>
+      </c>
+      <c r="K101" s="2">
         <v>5</v>
       </c>
-      <c r="K101" s="2">
+      <c r="L101" s="2">
         <v>3</v>
       </c>
-      <c r="L101" s="2"/>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M101" s="2"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>14</v>
       </c>
@@ -7524,20 +7891,23 @@
         <v>1</v>
       </c>
       <c r="H102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="2">
         <v>0</v>
       </c>
       <c r="J102" s="2">
+        <v>0</v>
+      </c>
+      <c r="K102" s="2">
         <v>1.5</v>
       </c>
-      <c r="K102" s="2">
+      <c r="L102" s="2">
         <v>1</v>
       </c>
-      <c r="L102" s="2"/>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M102" s="2"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>14</v>
       </c>
@@ -7560,20 +7930,23 @@
         <v>2.5</v>
       </c>
       <c r="H103" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I103" s="2">
         <v>0</v>
       </c>
       <c r="J103" s="2">
+        <v>0</v>
+      </c>
+      <c r="K103" s="2">
         <v>4</v>
       </c>
-      <c r="K103" s="2">
+      <c r="L103" s="2">
         <v>2.5</v>
       </c>
-      <c r="L103" s="2"/>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M103" s="2"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>14</v>
       </c>
@@ -7596,20 +7969,23 @@
         <v>5</v>
       </c>
       <c r="H104" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I104" s="2">
         <v>0</v>
       </c>
       <c r="J104" s="2">
+        <v>0</v>
+      </c>
+      <c r="K104" s="2">
         <v>10</v>
       </c>
-      <c r="K104" s="2">
+      <c r="L104" s="2">
         <v>5</v>
       </c>
-      <c r="L104" s="2"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M104" s="2"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>14</v>
       </c>
@@ -7632,20 +8008,23 @@
         <v>2</v>
       </c>
       <c r="H105" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I105" s="2">
         <v>0</v>
       </c>
       <c r="J105" s="2">
+        <v>0</v>
+      </c>
+      <c r="K105" s="2">
         <v>3</v>
       </c>
-      <c r="K105" s="2">
-        <v>2</v>
-      </c>
-      <c r="L105" s="2"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L105" s="2">
+        <v>2</v>
+      </c>
+      <c r="M105" s="2"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>14</v>
       </c>
@@ -7668,20 +8047,23 @@
         <v>5</v>
       </c>
       <c r="H106" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I106" s="2">
         <v>0</v>
       </c>
       <c r="J106" s="2">
+        <v>0</v>
+      </c>
+      <c r="K106" s="2">
         <v>10</v>
       </c>
-      <c r="K106" s="2">
+      <c r="L106" s="2">
         <v>5</v>
       </c>
-      <c r="L106" s="2"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M106" s="2"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>14</v>
       </c>
@@ -7704,20 +8086,23 @@
         <v>2</v>
       </c>
       <c r="H107" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I107" s="2">
         <v>0</v>
       </c>
       <c r="J107" s="2">
+        <v>0</v>
+      </c>
+      <c r="K107" s="2">
         <v>3</v>
       </c>
-      <c r="K107" s="2">
-        <v>2</v>
-      </c>
-      <c r="L107" s="2"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L107" s="2">
+        <v>2</v>
+      </c>
+      <c r="M107" s="2"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>14</v>
       </c>
@@ -7740,20 +8125,23 @@
         <v>1.5</v>
       </c>
       <c r="H108" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I108" s="2">
         <v>0</v>
       </c>
       <c r="J108" s="2">
+        <v>0</v>
+      </c>
+      <c r="K108" s="2">
         <v>3</v>
       </c>
-      <c r="K108" s="2">
+      <c r="L108" s="2">
         <v>1.5</v>
       </c>
-      <c r="L108" s="2"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M108" s="2"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>14</v>
       </c>
@@ -7776,20 +8164,23 @@
         <v>2.5</v>
       </c>
       <c r="H109" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I109" s="2">
         <v>0</v>
       </c>
       <c r="J109" s="2">
+        <v>0</v>
+      </c>
+      <c r="K109" s="2">
         <v>5</v>
       </c>
-      <c r="K109" s="2">
+      <c r="L109" s="2">
         <v>2.5</v>
       </c>
-      <c r="L109" s="2"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M109" s="2"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>14</v>
       </c>
@@ -7812,20 +8203,23 @@
         <v>2</v>
       </c>
       <c r="H110" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I110" s="2">
         <v>0</v>
       </c>
       <c r="J110" s="2">
+        <v>0</v>
+      </c>
+      <c r="K110" s="2">
         <v>4</v>
       </c>
-      <c r="K110" s="2">
-        <v>2</v>
-      </c>
-      <c r="L110" s="2"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L110" s="2">
+        <v>2</v>
+      </c>
+      <c r="M110" s="2"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>14</v>
       </c>
@@ -7848,20 +8242,23 @@
         <v>1.5</v>
       </c>
       <c r="H111" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I111" s="2">
         <v>0</v>
       </c>
       <c r="J111" s="2">
+        <v>0</v>
+      </c>
+      <c r="K111" s="2">
         <v>3</v>
       </c>
-      <c r="K111" s="2">
+      <c r="L111" s="2">
         <v>1.5</v>
       </c>
-      <c r="L111" s="2"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M111" s="2"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>14</v>
       </c>
@@ -7884,20 +8281,23 @@
         <v>1</v>
       </c>
       <c r="H112" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" s="2">
         <v>0</v>
       </c>
       <c r="J112" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K112" s="2">
+        <v>2</v>
+      </c>
+      <c r="L112" s="2">
         <v>1</v>
       </c>
-      <c r="L112" s="2"/>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M112" s="2"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>14</v>
       </c>
@@ -7920,20 +8320,23 @@
         <v>1</v>
       </c>
       <c r="H113" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" s="2">
         <v>0</v>
       </c>
       <c r="J113" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K113" s="2">
+        <v>2</v>
+      </c>
+      <c r="L113" s="2">
         <v>1</v>
       </c>
-      <c r="L113" s="2"/>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M113" s="2"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>14</v>
       </c>
@@ -7956,20 +8359,23 @@
         <v>0.5</v>
       </c>
       <c r="H114" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I114" s="2">
         <v>0</v>
       </c>
       <c r="J114" s="2">
+        <v>0</v>
+      </c>
+      <c r="K114" s="2">
         <v>1</v>
       </c>
-      <c r="K114" s="2">
+      <c r="L114" s="2">
         <v>0.5</v>
       </c>
-      <c r="L114" s="2"/>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M114" s="2"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>14</v>
       </c>
@@ -7992,20 +8398,23 @@
         <v>2</v>
       </c>
       <c r="H115" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I115" s="2">
         <v>0</v>
       </c>
       <c r="J115" s="2">
+        <v>0</v>
+      </c>
+      <c r="K115" s="2">
         <v>3</v>
       </c>
-      <c r="K115" s="2">
-        <v>2</v>
-      </c>
-      <c r="L115" s="2"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L115" s="2">
+        <v>2</v>
+      </c>
+      <c r="M115" s="2"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>14</v>
       </c>
@@ -8028,7 +8437,7 @@
         <v>3</v>
       </c>
       <c r="H116" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I116" s="2">
         <v>0</v>
@@ -8037,13 +8446,16 @@
         <v>0</v>
       </c>
       <c r="K116" s="2">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2">
         <v>3</v>
       </c>
-      <c r="L116" s="2" t="s">
+      <c r="M116" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>14</v>
       </c>
@@ -8066,7 +8478,7 @@
         <v>3</v>
       </c>
       <c r="H117" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I117" s="2">
         <v>0</v>
@@ -8075,11 +8487,14 @@
         <v>0</v>
       </c>
       <c r="K117" s="2">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2">
         <v>3</v>
       </c>
-      <c r="L117" s="2"/>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M117" s="2"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>14</v>
       </c>
@@ -8102,20 +8517,23 @@
         <v>1</v>
       </c>
       <c r="H118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="2">
         <v>0</v>
       </c>
       <c r="J118" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K118" s="2">
+        <v>2</v>
+      </c>
+      <c r="L118" s="2">
         <v>1</v>
       </c>
-      <c r="L118" s="2"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M118" s="2"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>14</v>
       </c>
@@ -8138,20 +8556,23 @@
         <v>4</v>
       </c>
       <c r="H119" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I119" s="2">
         <v>0</v>
       </c>
       <c r="J119" s="2">
+        <v>0</v>
+      </c>
+      <c r="K119" s="2">
         <v>8</v>
       </c>
-      <c r="K119" s="2">
+      <c r="L119" s="2">
         <v>4</v>
       </c>
-      <c r="L119" s="2"/>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M119" s="2"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>14</v>
       </c>
@@ -8174,20 +8595,23 @@
         <v>2.5</v>
       </c>
       <c r="H120" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I120" s="2">
         <v>0</v>
       </c>
       <c r="J120" s="2">
+        <v>0</v>
+      </c>
+      <c r="K120" s="2">
         <v>5</v>
       </c>
-      <c r="K120" s="2">
+      <c r="L120" s="2">
         <v>2.5</v>
       </c>
-      <c r="L120" s="2"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M120" s="2"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>14</v>
       </c>
@@ -8210,20 +8634,23 @@
         <v>2.5</v>
       </c>
       <c r="H121" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I121" s="2">
         <v>0</v>
       </c>
       <c r="J121" s="2">
+        <v>0</v>
+      </c>
+      <c r="K121" s="2">
         <v>6</v>
       </c>
-      <c r="K121" s="2">
+      <c r="L121" s="2">
         <v>2.5</v>
       </c>
-      <c r="L121" s="2"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M121" s="2"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>14</v>
       </c>
@@ -8246,20 +8673,23 @@
         <v>2</v>
       </c>
       <c r="H122" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I122" s="2">
         <v>0</v>
       </c>
       <c r="J122" s="2">
+        <v>0</v>
+      </c>
+      <c r="K122" s="2">
         <v>4</v>
       </c>
-      <c r="K122" s="2">
-        <v>2</v>
-      </c>
-      <c r="L122" s="2"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L122" s="2">
+        <v>2</v>
+      </c>
+      <c r="M122" s="2"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>14</v>
       </c>
@@ -8282,20 +8712,23 @@
         <v>3</v>
       </c>
       <c r="H123" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I123" s="2">
         <v>0</v>
       </c>
       <c r="J123" s="2">
+        <v>0</v>
+      </c>
+      <c r="K123" s="2">
         <v>5</v>
       </c>
-      <c r="K123" s="2">
+      <c r="L123" s="2">
         <v>3</v>
       </c>
-      <c r="L123" s="2"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M123" s="2"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>14</v>
       </c>
@@ -8318,20 +8751,23 @@
         <v>2</v>
       </c>
       <c r="H124" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I124" s="2">
         <v>0</v>
       </c>
       <c r="J124" s="2">
+        <v>0</v>
+      </c>
+      <c r="K124" s="2">
         <v>3</v>
       </c>
-      <c r="K124" s="2">
-        <v>2</v>
-      </c>
-      <c r="L124" s="2"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L124" s="2">
+        <v>2</v>
+      </c>
+      <c r="M124" s="2"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>14</v>
       </c>
@@ -8354,20 +8790,23 @@
         <v>2</v>
       </c>
       <c r="H125" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I125" s="2">
         <v>0</v>
       </c>
       <c r="J125" s="2">
+        <v>0</v>
+      </c>
+      <c r="K125" s="2">
         <v>3</v>
       </c>
-      <c r="K125" s="2">
-        <v>2</v>
-      </c>
-      <c r="L125" s="2"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L125" s="2">
+        <v>2</v>
+      </c>
+      <c r="M125" s="2"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>14</v>
       </c>
@@ -8390,20 +8829,23 @@
         <v>2</v>
       </c>
       <c r="H126" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I126" s="2">
         <v>0</v>
       </c>
       <c r="J126" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" s="2">
         <v>2</v>
       </c>
-      <c r="L126" s="2"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L126" s="2">
+        <v>2</v>
+      </c>
+      <c r="M126" s="2"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>14</v>
       </c>
@@ -8426,20 +8868,23 @@
         <v>2.5</v>
       </c>
       <c r="H127" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I127" s="2">
         <v>0</v>
       </c>
       <c r="J127" s="2">
+        <v>0</v>
+      </c>
+      <c r="K127" s="2">
         <v>3</v>
       </c>
-      <c r="K127" s="2">
+      <c r="L127" s="2">
         <v>2.5</v>
       </c>
-      <c r="L127" s="2"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M127" s="2"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>15</v>
       </c>
@@ -8462,20 +8907,23 @@
         <v>0.8</v>
       </c>
       <c r="H128" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I128" s="2">
         <v>0</v>
       </c>
       <c r="J128" s="2">
+        <v>0</v>
+      </c>
+      <c r="K128" s="2">
         <v>1.5</v>
       </c>
-      <c r="K128" s="2">
+      <c r="L128" s="2">
         <v>0.8</v>
       </c>
-      <c r="L128" s="2"/>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M128" s="2"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>15</v>
       </c>
@@ -8498,20 +8946,23 @@
         <v>4</v>
       </c>
       <c r="H129" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I129" s="2">
         <v>0</v>
       </c>
       <c r="J129" s="2">
+        <v>0</v>
+      </c>
+      <c r="K129" s="2">
         <v>8</v>
       </c>
-      <c r="K129" s="2">
+      <c r="L129" s="2">
         <v>4</v>
       </c>
-      <c r="L129" s="2"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M129" s="2"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>15</v>
       </c>
@@ -8534,20 +8985,23 @@
         <v>45</v>
       </c>
       <c r="H130" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I130" s="2">
         <v>0</v>
       </c>
       <c r="J130" s="2">
+        <v>0</v>
+      </c>
+      <c r="K130" s="2">
         <v>102</v>
       </c>
-      <c r="K130" s="2">
+      <c r="L130" s="2">
         <v>45</v>
       </c>
-      <c r="L130" s="2"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M130" s="2"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>15</v>
       </c>
@@ -8570,20 +9024,23 @@
         <v>32</v>
       </c>
       <c r="H131" s="2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I131" s="2">
         <v>0</v>
       </c>
       <c r="J131" s="2">
+        <v>0</v>
+      </c>
+      <c r="K131" s="2">
         <v>74</v>
       </c>
-      <c r="K131" s="2">
+      <c r="L131" s="2">
         <v>32</v>
       </c>
-      <c r="L131" s="2"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M131" s="2"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>15</v>
       </c>
@@ -8606,20 +9063,23 @@
         <v>19</v>
       </c>
       <c r="H132" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I132" s="2">
         <v>0</v>
       </c>
       <c r="J132" s="2">
+        <v>0</v>
+      </c>
+      <c r="K132" s="2">
         <v>46</v>
       </c>
-      <c r="K132" s="2">
+      <c r="L132" s="2">
         <v>19</v>
       </c>
-      <c r="L132" s="2"/>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M132" s="2"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>15</v>
       </c>
@@ -8642,20 +9102,23 @@
         <v>19</v>
       </c>
       <c r="H133" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I133" s="2">
         <v>0</v>
       </c>
       <c r="J133" s="2">
+        <v>0</v>
+      </c>
+      <c r="K133" s="2">
         <v>46</v>
       </c>
-      <c r="K133" s="2">
+      <c r="L133" s="2">
         <v>19</v>
       </c>
-      <c r="L133" s="2"/>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M133" s="2"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>15</v>
       </c>
@@ -8678,20 +9141,23 @@
         <v>19</v>
       </c>
       <c r="H134" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I134" s="2">
         <v>0</v>
       </c>
       <c r="J134" s="2">
+        <v>0</v>
+      </c>
+      <c r="K134" s="2">
         <v>46</v>
       </c>
-      <c r="K134" s="2">
+      <c r="L134" s="2">
         <v>19</v>
       </c>
-      <c r="L134" s="2"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M134" s="2"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>15</v>
       </c>
@@ -8714,20 +9180,23 @@
         <v>58</v>
       </c>
       <c r="H135" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I135" s="2">
         <v>0</v>
       </c>
       <c r="J135" s="2">
+        <v>0</v>
+      </c>
+      <c r="K135" s="2">
         <v>152</v>
       </c>
-      <c r="K135" s="2">
+      <c r="L135" s="2">
         <v>58</v>
       </c>
-      <c r="L135" s="2"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M135" s="2"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>15</v>
       </c>
@@ -8750,22 +9219,25 @@
         <v>16</v>
       </c>
       <c r="H136" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I136" s="2">
         <v>0</v>
       </c>
       <c r="J136" s="2">
+        <v>0</v>
+      </c>
+      <c r="K136" s="2">
         <v>20</v>
       </c>
-      <c r="K136" s="2">
+      <c r="L136" s="2">
         <v>16</v>
       </c>
-      <c r="L136" s="2" t="s">
+      <c r="M136" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>15</v>
       </c>
@@ -8788,20 +9260,23 @@
         <v>7</v>
       </c>
       <c r="H137" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I137" s="2">
         <v>0</v>
       </c>
       <c r="J137" s="2">
+        <v>0</v>
+      </c>
+      <c r="K137" s="2">
         <v>12</v>
       </c>
-      <c r="K137" s="2">
+      <c r="L137" s="2">
         <v>7</v>
       </c>
-      <c r="L137" s="2"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M137" s="2"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>15</v>
       </c>
@@ -8824,20 +9299,23 @@
         <v>5</v>
       </c>
       <c r="H138" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I138" s="2">
         <v>0</v>
       </c>
       <c r="J138" s="2">
+        <v>0</v>
+      </c>
+      <c r="K138" s="2">
         <v>8</v>
       </c>
-      <c r="K138" s="2">
+      <c r="L138" s="2">
         <v>5</v>
       </c>
-      <c r="L138" s="2"/>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M138" s="2"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>15</v>
       </c>
@@ -8860,20 +9338,23 @@
         <v>6</v>
       </c>
       <c r="H139" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I139" s="2">
         <v>0</v>
       </c>
       <c r="J139" s="2">
+        <v>0</v>
+      </c>
+      <c r="K139" s="2">
         <v>10</v>
       </c>
-      <c r="K139" s="2">
+      <c r="L139" s="2">
         <v>6</v>
       </c>
-      <c r="L139" s="2"/>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M139" s="2"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>15</v>
       </c>
@@ -8896,20 +9377,23 @@
         <v>7</v>
       </c>
       <c r="H140" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I140" s="2">
         <v>0</v>
       </c>
       <c r="J140" s="2">
+        <v>0</v>
+      </c>
+      <c r="K140" s="2">
         <v>12</v>
       </c>
-      <c r="K140" s="2">
+      <c r="L140" s="2">
         <v>7</v>
       </c>
-      <c r="L140" s="2"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M140" s="2"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>15</v>
       </c>
@@ -8932,20 +9416,23 @@
         <v>5</v>
       </c>
       <c r="H141" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I141" s="2">
         <v>0</v>
       </c>
       <c r="J141" s="2">
+        <v>0</v>
+      </c>
+      <c r="K141" s="2">
         <v>6</v>
       </c>
-      <c r="K141" s="2">
+      <c r="L141" s="2">
         <v>5</v>
       </c>
-      <c r="L141" s="2"/>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M141" s="2"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>15</v>
       </c>
@@ -8968,20 +9455,23 @@
         <v>3.5</v>
       </c>
       <c r="H142" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I142" s="2">
         <v>0</v>
       </c>
       <c r="J142" s="2">
+        <v>0</v>
+      </c>
+      <c r="K142" s="2">
         <v>4</v>
       </c>
-      <c r="K142" s="2">
+      <c r="L142" s="2">
         <v>3.5</v>
       </c>
-      <c r="L142" s="2"/>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M142" s="2"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>16</v>
       </c>
@@ -9004,20 +9494,23 @@
         <v>1.5</v>
       </c>
       <c r="H143" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I143" s="2">
         <v>0</v>
       </c>
       <c r="J143" s="2">
+        <v>0</v>
+      </c>
+      <c r="K143" s="2">
         <v>3</v>
       </c>
-      <c r="K143" s="2">
+      <c r="L143" s="2">
         <v>1.5</v>
       </c>
-      <c r="L143" s="2"/>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M143" s="2"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>16</v>
       </c>
@@ -9040,22 +9533,25 @@
         <v>2.5</v>
       </c>
       <c r="H144" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I144" s="2">
         <v>1.5</v>
       </c>
-      <c r="I144" s="2">
+      <c r="J144" s="2">
         <v>0.75</v>
       </c>
-      <c r="J144" s="2">
+      <c r="K144" s="2">
         <v>3.5</v>
       </c>
-      <c r="K144" s="2">
+      <c r="L144" s="2">
         <v>1.75</v>
       </c>
-      <c r="L144" s="2" t="s">
+      <c r="M144" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>16</v>
       </c>
@@ -9078,20 +9574,23 @@
         <v>2</v>
       </c>
       <c r="H145" s="2">
+        <v>2</v>
+      </c>
+      <c r="I145" s="2">
         <v>1</v>
       </c>
-      <c r="I145" s="2">
+      <c r="J145" s="2">
         <v>0.5</v>
       </c>
-      <c r="J145" s="2">
+      <c r="K145" s="2">
         <v>3</v>
       </c>
-      <c r="K145" s="2">
+      <c r="L145" s="2">
         <v>1.5</v>
       </c>
-      <c r="L145" s="2"/>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M145" s="2"/>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>16</v>
       </c>
@@ -9114,20 +9613,23 @@
         <v>1.5</v>
       </c>
       <c r="H146" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I146" s="2">
         <v>1.2</v>
       </c>
-      <c r="I146" s="2">
+      <c r="J146" s="2">
         <v>0.6</v>
       </c>
-      <c r="J146" s="2">
+      <c r="K146" s="2">
         <v>1.8</v>
       </c>
-      <c r="K146" s="2">
+      <c r="L146" s="2">
         <v>0.9</v>
       </c>
-      <c r="L146" s="2"/>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M146" s="2"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>16</v>
       </c>
@@ -9150,20 +9652,23 @@
         <v>1.5</v>
       </c>
       <c r="H147" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I147" s="2">
         <v>0.9</v>
       </c>
-      <c r="I147" s="2">
+      <c r="J147" s="2">
         <v>0.45</v>
       </c>
-      <c r="J147" s="2">
+      <c r="K147" s="2">
         <v>2.1</v>
       </c>
-      <c r="K147" s="2">
+      <c r="L147" s="2">
         <v>1.05</v>
       </c>
-      <c r="L147" s="2"/>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M147" s="2"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>16</v>
       </c>
@@ -9186,20 +9691,23 @@
         <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I148" s="2">
         <v>0</v>
       </c>
       <c r="J148" s="2">
+        <v>0</v>
+      </c>
+      <c r="K148" s="2">
         <v>4</v>
       </c>
-      <c r="K148" s="2">
-        <v>2</v>
-      </c>
-      <c r="L148" s="2"/>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L148" s="2">
+        <v>2</v>
+      </c>
+      <c r="M148" s="2"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>16</v>
       </c>
@@ -9222,20 +9730,23 @@
         <v>1.5</v>
       </c>
       <c r="H149" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I149" s="2">
         <v>0</v>
       </c>
       <c r="J149" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K149" s="2">
+        <v>2</v>
+      </c>
+      <c r="L149" s="2">
         <v>1.5</v>
       </c>
-      <c r="L149" s="2"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M149" s="2"/>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>16</v>
       </c>
@@ -9258,20 +9769,23 @@
         <v>1.5</v>
       </c>
       <c r="H150" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I150" s="2">
         <v>0</v>
       </c>
       <c r="J150" s="2">
+        <v>0</v>
+      </c>
+      <c r="K150" s="2">
         <v>3</v>
       </c>
-      <c r="K150" s="2">
+      <c r="L150" s="2">
         <v>1.5</v>
       </c>
-      <c r="L150" s="2"/>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M150" s="2"/>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>16</v>
       </c>
@@ -9294,20 +9808,23 @@
         <v>3</v>
       </c>
       <c r="H151" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I151" s="2">
         <v>0</v>
       </c>
       <c r="J151" s="2">
+        <v>0</v>
+      </c>
+      <c r="K151" s="2">
         <v>6</v>
       </c>
-      <c r="K151" s="2">
+      <c r="L151" s="2">
         <v>3</v>
       </c>
-      <c r="L151" s="2"/>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M151" s="2"/>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>16</v>
       </c>
@@ -9330,20 +9847,23 @@
         <v>0.8</v>
       </c>
       <c r="H152" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I152" s="2">
         <v>0</v>
       </c>
       <c r="J152" s="2">
+        <v>0</v>
+      </c>
+      <c r="K152" s="2">
         <v>1.5</v>
       </c>
-      <c r="K152" s="2">
+      <c r="L152" s="2">
         <v>0.8</v>
       </c>
-      <c r="L152" s="2"/>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M152" s="2"/>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>16</v>
       </c>
@@ -9366,20 +9886,23 @@
         <v>0.8</v>
       </c>
       <c r="H153" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I153" s="2">
         <v>0</v>
       </c>
       <c r="J153" s="2">
+        <v>0</v>
+      </c>
+      <c r="K153" s="2">
         <v>1.5</v>
       </c>
-      <c r="K153" s="2">
+      <c r="L153" s="2">
         <v>0.8</v>
       </c>
-      <c r="L153" s="2"/>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M153" s="2"/>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>16</v>
       </c>
@@ -9402,20 +9925,23 @@
         <v>0.5</v>
       </c>
       <c r="H154" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I154" s="2">
         <v>0</v>
       </c>
       <c r="J154" s="2">
+        <v>0</v>
+      </c>
+      <c r="K154" s="2">
         <v>1</v>
       </c>
-      <c r="K154" s="2">
+      <c r="L154" s="2">
         <v>0.5</v>
       </c>
-      <c r="L154" s="2"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M154" s="2"/>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>16</v>
       </c>
@@ -9438,20 +9964,23 @@
         <v>2</v>
       </c>
       <c r="H155" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I155" s="2">
         <v>0</v>
       </c>
       <c r="J155" s="2">
+        <v>0</v>
+      </c>
+      <c r="K155" s="2">
         <v>3</v>
       </c>
-      <c r="K155" s="2">
-        <v>2</v>
-      </c>
-      <c r="L155" s="2"/>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L155" s="2">
+        <v>2</v>
+      </c>
+      <c r="M155" s="2"/>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>16</v>
       </c>
@@ -9474,7 +10003,7 @@
         <v>2.5</v>
       </c>
       <c r="H156" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I156" s="2">
         <v>0</v>
@@ -9483,11 +10012,14 @@
         <v>0</v>
       </c>
       <c r="K156" s="2">
+        <v>0</v>
+      </c>
+      <c r="L156" s="2">
         <v>2.5</v>
       </c>
-      <c r="L156" s="2"/>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M156" s="2"/>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>16</v>
       </c>
@@ -9510,7 +10042,7 @@
         <v>2.5</v>
       </c>
       <c r="H157" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I157" s="2">
         <v>0</v>
@@ -9519,11 +10051,14 @@
         <v>0</v>
       </c>
       <c r="K157" s="2">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2">
         <v>2.5</v>
       </c>
-      <c r="L157" s="2"/>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M157" s="2"/>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>16</v>
       </c>
@@ -9546,20 +10081,23 @@
         <v>0.8</v>
       </c>
       <c r="H158" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I158" s="2">
         <v>0</v>
       </c>
       <c r="J158" s="2">
+        <v>0</v>
+      </c>
+      <c r="K158" s="2">
         <v>1.5</v>
       </c>
-      <c r="K158" s="2">
+      <c r="L158" s="2">
         <v>0.8</v>
       </c>
-      <c r="L158" s="2"/>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M158" s="2"/>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>16</v>
       </c>
@@ -9582,22 +10120,25 @@
         <v>1</v>
       </c>
       <c r="H159" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" s="2">
         <v>0</v>
       </c>
       <c r="J159" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159" s="2">
+        <v>2</v>
+      </c>
+      <c r="L159" s="2">
         <v>1</v>
       </c>
-      <c r="L159" s="2" t="s">
+      <c r="M159" s="2" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>16</v>
       </c>
@@ -9620,20 +10161,23 @@
         <v>1</v>
       </c>
       <c r="H160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" s="2">
         <v>0</v>
       </c>
       <c r="J160" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K160" s="2">
+        <v>2</v>
+      </c>
+      <c r="L160" s="2">
         <v>1</v>
       </c>
-      <c r="L160" s="2"/>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M160" s="2"/>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
         <v>16</v>
       </c>
@@ -9656,20 +10200,23 @@
         <v>1.5</v>
       </c>
       <c r="H161" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I161" s="2">
         <v>0</v>
       </c>
       <c r="J161" s="2">
+        <v>0</v>
+      </c>
+      <c r="K161" s="2">
         <v>4</v>
       </c>
-      <c r="K161" s="2">
+      <c r="L161" s="2">
         <v>1.5</v>
       </c>
-      <c r="L161" s="2"/>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M161" s="2"/>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>16</v>
       </c>
@@ -9692,20 +10239,23 @@
         <v>1</v>
       </c>
       <c r="H162" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="2">
         <v>0</v>
       </c>
       <c r="J162" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K162" s="2">
+        <v>2</v>
+      </c>
+      <c r="L162" s="2">
         <v>1</v>
       </c>
-      <c r="L162" s="2"/>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M162" s="2"/>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>16</v>
       </c>
@@ -9728,20 +10278,23 @@
         <v>2</v>
       </c>
       <c r="H163" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I163" s="2">
         <v>0</v>
       </c>
       <c r="J163" s="2">
+        <v>0</v>
+      </c>
+      <c r="K163" s="2">
         <v>3</v>
       </c>
-      <c r="K163" s="2">
-        <v>2</v>
-      </c>
-      <c r="L163" s="2"/>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L163" s="2">
+        <v>2</v>
+      </c>
+      <c r="M163" s="2"/>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>16</v>
       </c>
@@ -9764,20 +10317,23 @@
         <v>1.5</v>
       </c>
       <c r="H164" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I164" s="2">
         <v>0</v>
       </c>
       <c r="J164" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K164" s="2">
+        <v>2</v>
+      </c>
+      <c r="L164" s="2">
         <v>1.5</v>
       </c>
-      <c r="L164" s="2"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M164" s="2"/>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>16</v>
       </c>
@@ -9800,20 +10356,23 @@
         <v>1.5</v>
       </c>
       <c r="H165" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I165" s="2">
         <v>0</v>
       </c>
       <c r="J165" s="2">
+        <v>0</v>
+      </c>
+      <c r="K165" s="2">
         <v>2.5</v>
       </c>
-      <c r="K165" s="2">
+      <c r="L165" s="2">
         <v>1.5</v>
       </c>
-      <c r="L165" s="2"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M165" s="2"/>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>16</v>
       </c>
@@ -9836,20 +10395,23 @@
         <v>2</v>
       </c>
       <c r="H166" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I166" s="2">
         <v>0</v>
       </c>
       <c r="J166" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K166" s="2">
         <v>2</v>
       </c>
-      <c r="L166" s="2"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L166" s="2">
+        <v>2</v>
+      </c>
+      <c r="M166" s="2"/>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
         <v>16</v>
       </c>
@@ -9872,20 +10434,23 @@
         <v>2.5</v>
       </c>
       <c r="H167" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I167" s="2">
         <v>0</v>
       </c>
       <c r="J167" s="2">
+        <v>0</v>
+      </c>
+      <c r="K167" s="2">
         <v>3</v>
       </c>
-      <c r="K167" s="2">
+      <c r="L167" s="2">
         <v>2.5</v>
       </c>
-      <c r="L167" s="2"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M167" s="2"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
         <v>17</v>
       </c>
@@ -9908,20 +10473,23 @@
         <v>0.5</v>
       </c>
       <c r="H168" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I168" s="2">
         <v>0</v>
       </c>
       <c r="J168" s="2">
+        <v>0</v>
+      </c>
+      <c r="K168" s="2">
         <v>1</v>
       </c>
-      <c r="K168" s="2">
+      <c r="L168" s="2">
         <v>0.5</v>
       </c>
-      <c r="L168" s="2"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M168" s="2"/>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
         <v>17</v>
       </c>
@@ -9944,20 +10512,23 @@
         <v>2</v>
       </c>
       <c r="H169" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I169" s="2">
         <v>0</v>
       </c>
       <c r="J169" s="2">
+        <v>0</v>
+      </c>
+      <c r="K169" s="2">
         <v>4</v>
       </c>
-      <c r="K169" s="2">
-        <v>2</v>
-      </c>
-      <c r="L169" s="2"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L169" s="2">
+        <v>2</v>
+      </c>
+      <c r="M169" s="2"/>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
         <v>17</v>
       </c>
@@ -9980,20 +10551,23 @@
         <v>13.8</v>
       </c>
       <c r="H170" s="2">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I170" s="2">
         <v>0</v>
       </c>
       <c r="J170" s="2">
+        <v>0</v>
+      </c>
+      <c r="K170" s="2">
         <v>36</v>
       </c>
-      <c r="K170" s="2">
+      <c r="L170" s="2">
         <v>13.8</v>
       </c>
-      <c r="L170" s="2"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M170" s="2"/>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
         <v>17</v>
       </c>
@@ -10016,20 +10590,23 @@
         <v>10</v>
       </c>
       <c r="H171" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I171" s="2">
         <v>0</v>
       </c>
       <c r="J171" s="2">
+        <v>0</v>
+      </c>
+      <c r="K171" s="2">
         <v>26.5</v>
       </c>
-      <c r="K171" s="2">
+      <c r="L171" s="2">
         <v>10</v>
       </c>
-      <c r="L171" s="2"/>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M171" s="2"/>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="5" t="s">
         <v>17</v>
       </c>
@@ -10052,20 +10629,23 @@
         <v>6.2</v>
       </c>
       <c r="H172" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I172" s="2">
         <v>0</v>
       </c>
       <c r="J172" s="2">
+        <v>0</v>
+      </c>
+      <c r="K172" s="2">
         <v>17</v>
       </c>
-      <c r="K172" s="2">
+      <c r="L172" s="2">
         <v>6.2</v>
       </c>
-      <c r="L172" s="2"/>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M172" s="2"/>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
         <v>17</v>
       </c>
@@ -10088,20 +10668,23 @@
         <v>6.2</v>
       </c>
       <c r="H173" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I173" s="2">
         <v>0</v>
       </c>
       <c r="J173" s="2">
+        <v>0</v>
+      </c>
+      <c r="K173" s="2">
         <v>17</v>
       </c>
-      <c r="K173" s="2">
+      <c r="L173" s="2">
         <v>6.2</v>
       </c>
-      <c r="L173" s="2"/>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M173" s="2"/>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
         <v>17</v>
       </c>
@@ -10124,20 +10707,23 @@
         <v>6.2</v>
       </c>
       <c r="H174" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I174" s="2">
         <v>0</v>
       </c>
       <c r="J174" s="2">
+        <v>0</v>
+      </c>
+      <c r="K174" s="2">
         <v>17</v>
       </c>
-      <c r="K174" s="2">
+      <c r="L174" s="2">
         <v>6.2</v>
       </c>
-      <c r="L174" s="2"/>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M174" s="2"/>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
         <v>17</v>
       </c>
@@ -10160,20 +10746,23 @@
         <v>20.399999999999999</v>
       </c>
       <c r="H175" s="2">
-        <v>0</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="I175" s="2">
         <v>0</v>
       </c>
       <c r="J175" s="2">
+        <v>0</v>
+      </c>
+      <c r="K175" s="2">
         <v>59</v>
       </c>
-      <c r="K175" s="2">
+      <c r="L175" s="2">
         <v>20.399999999999999</v>
       </c>
-      <c r="L175" s="2"/>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M175" s="2"/>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="5" t="s">
         <v>17</v>
       </c>
@@ -10196,20 +10785,23 @@
         <v>10</v>
       </c>
       <c r="H176" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I176" s="2">
         <v>0</v>
       </c>
       <c r="J176" s="2">
+        <v>0</v>
+      </c>
+      <c r="K176" s="2">
         <v>12</v>
       </c>
-      <c r="K176" s="2">
+      <c r="L176" s="2">
         <v>10</v>
       </c>
-      <c r="L176" s="2"/>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M176" s="2"/>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
         <v>17</v>
       </c>
@@ -10232,20 +10824,23 @@
         <v>5</v>
       </c>
       <c r="H177" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I177" s="2">
         <v>0</v>
       </c>
       <c r="J177" s="2">
+        <v>0</v>
+      </c>
+      <c r="K177" s="2">
         <v>8</v>
       </c>
-      <c r="K177" s="2">
+      <c r="L177" s="2">
         <v>5</v>
       </c>
-      <c r="L177" s="2"/>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M177" s="2"/>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
         <v>17</v>
       </c>
@@ -10268,20 +10863,23 @@
         <v>5</v>
       </c>
       <c r="H178" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I178" s="2">
         <v>0</v>
       </c>
       <c r="J178" s="2">
+        <v>0</v>
+      </c>
+      <c r="K178" s="2">
         <v>8</v>
       </c>
-      <c r="K178" s="2">
+      <c r="L178" s="2">
         <v>5</v>
       </c>
-      <c r="L178" s="2"/>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M178" s="2"/>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="5" t="s">
         <v>17</v>
       </c>
@@ -10304,20 +10902,23 @@
         <v>5</v>
       </c>
       <c r="H179" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I179" s="2">
         <v>0</v>
       </c>
       <c r="J179" s="2">
+        <v>0</v>
+      </c>
+      <c r="K179" s="2">
         <v>8</v>
       </c>
-      <c r="K179" s="2">
+      <c r="L179" s="2">
         <v>5</v>
       </c>
-      <c r="L179" s="2"/>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M179" s="2"/>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>17</v>
       </c>
@@ -10340,20 +10941,23 @@
         <v>6</v>
       </c>
       <c r="H180" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I180" s="2">
         <v>0</v>
       </c>
       <c r="J180" s="2">
+        <v>0</v>
+      </c>
+      <c r="K180" s="2">
         <v>10</v>
       </c>
-      <c r="K180" s="2">
+      <c r="L180" s="2">
         <v>6</v>
       </c>
-      <c r="L180" s="2"/>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M180" s="2"/>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>17</v>
       </c>
@@ -10376,20 +10980,23 @@
         <v>4</v>
       </c>
       <c r="H181" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I181" s="2">
         <v>0</v>
       </c>
       <c r="J181" s="2">
+        <v>0</v>
+      </c>
+      <c r="K181" s="2">
         <v>5</v>
       </c>
-      <c r="K181" s="2">
+      <c r="L181" s="2">
         <v>4</v>
       </c>
-      <c r="L181" s="2"/>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M181" s="2"/>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>18</v>
       </c>
@@ -10412,20 +11019,23 @@
         <v>3.5</v>
       </c>
       <c r="H182" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I182" s="2">
         <v>0</v>
       </c>
       <c r="J182" s="2">
+        <v>0</v>
+      </c>
+      <c r="K182" s="2">
         <v>6</v>
       </c>
-      <c r="K182" s="2">
+      <c r="L182" s="2">
         <v>3.5</v>
       </c>
-      <c r="L182" s="2"/>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M182" s="2"/>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>18</v>
       </c>
@@ -10448,20 +11058,23 @@
         <v>5</v>
       </c>
       <c r="H183" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I183" s="2">
         <v>0</v>
       </c>
       <c r="J183" s="2">
+        <v>0</v>
+      </c>
+      <c r="K183" s="2">
         <v>10</v>
       </c>
-      <c r="K183" s="2">
+      <c r="L183" s="2">
         <v>5</v>
       </c>
-      <c r="L183" s="2"/>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M183" s="2"/>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>18</v>
       </c>
@@ -10484,20 +11097,23 @@
         <v>4</v>
       </c>
       <c r="H184" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I184" s="2">
         <v>0</v>
       </c>
       <c r="J184" s="2">
+        <v>0</v>
+      </c>
+      <c r="K184" s="2">
         <v>8</v>
       </c>
-      <c r="K184" s="2">
+      <c r="L184" s="2">
         <v>4</v>
       </c>
-      <c r="L184" s="2"/>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M184" s="2"/>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>18</v>
       </c>
@@ -10520,20 +11136,23 @@
         <v>1.5</v>
       </c>
       <c r="H185" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I185" s="2">
         <v>0</v>
       </c>
       <c r="J185" s="2">
+        <v>0</v>
+      </c>
+      <c r="K185" s="2">
         <v>3</v>
       </c>
-      <c r="K185" s="2">
+      <c r="L185" s="2">
         <v>1.5</v>
       </c>
-      <c r="L185" s="2"/>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M185" s="2"/>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
         <v>18</v>
       </c>
@@ -10556,20 +11175,23 @@
         <v>5</v>
       </c>
       <c r="H186" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I186" s="2">
         <v>0</v>
       </c>
       <c r="J186" s="2">
+        <v>0</v>
+      </c>
+      <c r="K186" s="2">
         <v>10</v>
       </c>
-      <c r="K186" s="2">
+      <c r="L186" s="2">
         <v>5</v>
       </c>
-      <c r="L186" s="2"/>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M186" s="2"/>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="5" t="s">
         <v>18</v>
       </c>
@@ -10592,20 +11214,23 @@
         <v>4</v>
       </c>
       <c r="H187" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I187" s="2">
         <v>0</v>
       </c>
       <c r="J187" s="2">
+        <v>0</v>
+      </c>
+      <c r="K187" s="2">
         <v>8</v>
       </c>
-      <c r="K187" s="2">
+      <c r="L187" s="2">
         <v>4</v>
       </c>
-      <c r="L187" s="2"/>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M187" s="2"/>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
         <v>18</v>
       </c>
@@ -10628,20 +11253,23 @@
         <v>2</v>
       </c>
       <c r="H188" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I188" s="2">
         <v>0</v>
       </c>
       <c r="J188" s="2">
+        <v>0</v>
+      </c>
+      <c r="K188" s="2">
         <v>4</v>
       </c>
-      <c r="K188" s="2">
-        <v>2</v>
-      </c>
-      <c r="L188" s="2"/>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L188" s="2">
+        <v>2</v>
+      </c>
+      <c r="M188" s="2"/>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
         <v>18</v>
       </c>
@@ -10664,20 +11292,23 @@
         <v>3</v>
       </c>
       <c r="H189" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I189" s="2">
         <v>0</v>
       </c>
       <c r="J189" s="2">
+        <v>0</v>
+      </c>
+      <c r="K189" s="2">
         <v>5</v>
       </c>
-      <c r="K189" s="2">
+      <c r="L189" s="2">
         <v>3</v>
       </c>
-      <c r="L189" s="2"/>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M189" s="2"/>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
         <v>18</v>
       </c>
@@ -10700,20 +11331,23 @@
         <v>3</v>
       </c>
       <c r="H190" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I190" s="2">
         <v>0</v>
       </c>
       <c r="J190" s="2">
+        <v>0</v>
+      </c>
+      <c r="K190" s="2">
         <v>5</v>
       </c>
-      <c r="K190" s="2">
+      <c r="L190" s="2">
         <v>3</v>
       </c>
-      <c r="L190" s="2"/>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M190" s="2"/>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="5" t="s">
         <v>18</v>
       </c>
@@ -10736,20 +11370,23 @@
         <v>3.5</v>
       </c>
       <c r="H191" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I191" s="2">
         <v>0</v>
       </c>
       <c r="J191" s="2">
+        <v>0</v>
+      </c>
+      <c r="K191" s="2">
         <v>4</v>
       </c>
-      <c r="K191" s="2">
+      <c r="L191" s="2">
         <v>3.5</v>
       </c>
-      <c r="L191" s="2"/>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M191" s="2"/>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="5" t="s">
         <v>18</v>
       </c>
@@ -10772,20 +11409,23 @@
         <v>2.5</v>
       </c>
       <c r="H192" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I192" s="2">
         <v>0</v>
       </c>
       <c r="J192" s="2">
+        <v>0</v>
+      </c>
+      <c r="K192" s="2">
         <v>3</v>
       </c>
-      <c r="K192" s="2">
+      <c r="L192" s="2">
         <v>2.5</v>
       </c>
-      <c r="L192" s="2"/>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M192" s="2"/>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="5" t="s">
         <v>19</v>
       </c>
@@ -10808,20 +11448,23 @@
         <v>2.5</v>
       </c>
       <c r="H193" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I193" s="2">
         <v>0</v>
       </c>
       <c r="J193" s="2">
+        <v>0</v>
+      </c>
+      <c r="K193" s="2">
         <v>5</v>
       </c>
-      <c r="K193" s="2">
+      <c r="L193" s="2">
         <v>2.5</v>
       </c>
-      <c r="L193" s="2"/>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M193" s="2"/>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
         <v>19</v>
       </c>
@@ -10844,20 +11487,23 @@
         <v>2</v>
       </c>
       <c r="H194" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I194" s="2">
         <v>0</v>
       </c>
       <c r="J194" s="2">
+        <v>0</v>
+      </c>
+      <c r="K194" s="2">
         <v>4</v>
       </c>
-      <c r="K194" s="2">
-        <v>2</v>
-      </c>
-      <c r="L194" s="2"/>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L194" s="2">
+        <v>2</v>
+      </c>
+      <c r="M194" s="2"/>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="5" t="s">
         <v>19</v>
       </c>
@@ -10880,20 +11526,23 @@
         <v>2</v>
       </c>
       <c r="H195" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I195" s="2">
         <v>0</v>
       </c>
       <c r="J195" s="2">
+        <v>0</v>
+      </c>
+      <c r="K195" s="2">
         <v>4</v>
       </c>
-      <c r="K195" s="2">
-        <v>2</v>
-      </c>
-      <c r="L195" s="2"/>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L195" s="2">
+        <v>2</v>
+      </c>
+      <c r="M195" s="2"/>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="5" t="s">
         <v>19</v>
       </c>
@@ -10916,20 +11565,23 @@
         <v>3</v>
       </c>
       <c r="H196" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I196" s="2">
         <v>0</v>
       </c>
       <c r="J196" s="2">
+        <v>0</v>
+      </c>
+      <c r="K196" s="2">
         <v>6</v>
       </c>
-      <c r="K196" s="2">
+      <c r="L196" s="2">
         <v>3</v>
       </c>
-      <c r="L196" s="2"/>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M196" s="2"/>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="5" t="s">
         <v>19</v>
       </c>
@@ -10952,20 +11604,23 @@
         <v>1.5</v>
       </c>
       <c r="H197" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I197" s="2">
         <v>0</v>
       </c>
       <c r="J197" s="2">
+        <v>0</v>
+      </c>
+      <c r="K197" s="2">
         <v>3</v>
       </c>
-      <c r="K197" s="2">
+      <c r="L197" s="2">
         <v>1.5</v>
       </c>
-      <c r="L197" s="2"/>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M197" s="2"/>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
         <v>19</v>
       </c>
@@ -10988,20 +11643,23 @@
         <v>0.8</v>
       </c>
       <c r="H198" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I198" s="2">
         <v>0</v>
       </c>
       <c r="J198" s="2">
+        <v>0</v>
+      </c>
+      <c r="K198" s="2">
         <v>1.5</v>
       </c>
-      <c r="K198" s="2">
+      <c r="L198" s="2">
         <v>0.8</v>
       </c>
-      <c r="L198" s="2"/>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M198" s="2"/>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
         <v>19</v>
       </c>
@@ -11024,20 +11682,23 @@
         <v>2.5</v>
       </c>
       <c r="H199" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I199" s="2">
         <v>0</v>
       </c>
       <c r="J199" s="2">
+        <v>0</v>
+      </c>
+      <c r="K199" s="2">
         <v>4</v>
       </c>
-      <c r="K199" s="2">
+      <c r="L199" s="2">
         <v>2.5</v>
       </c>
-      <c r="L199" s="2"/>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M199" s="2"/>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="5" t="s">
         <v>19</v>
       </c>
@@ -11060,20 +11721,23 @@
         <v>2</v>
       </c>
       <c r="H200" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I200" s="2">
         <v>0</v>
       </c>
       <c r="J200" s="2">
+        <v>0</v>
+      </c>
+      <c r="K200" s="2">
         <v>3</v>
       </c>
-      <c r="K200" s="2">
-        <v>2</v>
-      </c>
-      <c r="L200" s="2"/>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L200" s="2">
+        <v>2</v>
+      </c>
+      <c r="M200" s="2"/>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="5" t="s">
         <v>19</v>
       </c>
@@ -11096,20 +11760,23 @@
         <v>2</v>
       </c>
       <c r="H201" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I201" s="2">
         <v>0</v>
       </c>
       <c r="J201" s="2">
+        <v>0</v>
+      </c>
+      <c r="K201" s="2">
         <v>3</v>
       </c>
-      <c r="K201" s="2">
-        <v>2</v>
-      </c>
-      <c r="L201" s="2"/>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L201" s="2">
+        <v>2</v>
+      </c>
+      <c r="M201" s="2"/>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
         <v>19</v>
       </c>
@@ -11132,20 +11799,23 @@
         <v>2</v>
       </c>
       <c r="H202" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I202" s="2">
         <v>0</v>
       </c>
       <c r="J202" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K202" s="2">
         <v>2</v>
       </c>
-      <c r="L202" s="2"/>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L202" s="2">
+        <v>2</v>
+      </c>
+      <c r="M202" s="2"/>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
         <v>19</v>
       </c>
@@ -11168,20 +11838,23 @@
         <v>1.5</v>
       </c>
       <c r="H203" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I203" s="2">
         <v>0</v>
       </c>
       <c r="J203" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K203" s="2">
+        <v>2</v>
+      </c>
+      <c r="L203" s="2">
         <v>1.5</v>
       </c>
-      <c r="L203" s="2"/>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M203" s="2"/>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
         <v>20</v>
       </c>
@@ -11204,20 +11877,23 @@
         <v>3</v>
       </c>
       <c r="H204" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I204" s="2">
         <v>0</v>
       </c>
       <c r="J204" s="2">
+        <v>0</v>
+      </c>
+      <c r="K204" s="2">
         <v>5</v>
       </c>
-      <c r="K204" s="2">
+      <c r="L204" s="2">
         <v>3</v>
       </c>
-      <c r="L204" s="2"/>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M204" s="2"/>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>20</v>
       </c>
@@ -11240,20 +11916,23 @@
         <v>2</v>
       </c>
       <c r="H205" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I205" s="2">
         <v>0</v>
       </c>
       <c r="J205" s="2">
+        <v>0</v>
+      </c>
+      <c r="K205" s="2">
         <v>4</v>
       </c>
-      <c r="K205" s="2">
-        <v>2</v>
-      </c>
-      <c r="L205" s="2"/>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L205" s="2">
+        <v>2</v>
+      </c>
+      <c r="M205" s="2"/>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
         <v>20</v>
       </c>
@@ -11276,20 +11955,23 @@
         <v>4</v>
       </c>
       <c r="H206" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I206" s="2">
         <v>0</v>
       </c>
       <c r="J206" s="2">
+        <v>0</v>
+      </c>
+      <c r="K206" s="2">
         <v>8</v>
       </c>
-      <c r="K206" s="2">
+      <c r="L206" s="2">
         <v>4</v>
       </c>
-      <c r="L206" s="2"/>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M206" s="2"/>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
         <v>20</v>
       </c>
@@ -11312,20 +11994,23 @@
         <v>1.5</v>
       </c>
       <c r="H207" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I207" s="2">
         <v>0</v>
       </c>
       <c r="J207" s="2">
+        <v>0</v>
+      </c>
+      <c r="K207" s="2">
         <v>3</v>
       </c>
-      <c r="K207" s="2">
+      <c r="L207" s="2">
         <v>1.5</v>
       </c>
-      <c r="L207" s="2"/>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M207" s="2"/>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="5" t="s">
         <v>20</v>
       </c>
@@ -11348,20 +12033,23 @@
         <v>4</v>
       </c>
       <c r="H208" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I208" s="2">
         <v>0</v>
       </c>
       <c r="J208" s="2">
+        <v>0</v>
+      </c>
+      <c r="K208" s="2">
         <v>8</v>
       </c>
-      <c r="K208" s="2">
+      <c r="L208" s="2">
         <v>4</v>
       </c>
-      <c r="L208" s="2"/>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M208" s="2"/>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
         <v>20</v>
       </c>
@@ -11384,20 +12072,23 @@
         <v>3</v>
       </c>
       <c r="H209" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I209" s="2">
         <v>0</v>
       </c>
       <c r="J209" s="2">
+        <v>0</v>
+      </c>
+      <c r="K209" s="2">
         <v>6</v>
       </c>
-      <c r="K209" s="2">
+      <c r="L209" s="2">
         <v>3</v>
       </c>
-      <c r="L209" s="2"/>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M209" s="2"/>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
         <v>20</v>
       </c>
@@ -11420,22 +12111,25 @@
         <v>14</v>
       </c>
       <c r="H210" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I210" s="2">
         <v>0</v>
       </c>
       <c r="J210" s="2">
+        <v>0</v>
+      </c>
+      <c r="K210" s="2">
         <v>36</v>
       </c>
-      <c r="K210" s="2">
+      <c r="L210" s="2">
         <v>14</v>
       </c>
-      <c r="L210" s="2" t="s">
+      <c r="M210" s="2" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
         <v>20</v>
       </c>
@@ -11458,20 +12152,23 @@
         <v>1.5</v>
       </c>
       <c r="H211" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I211" s="2">
         <v>0</v>
       </c>
       <c r="J211" s="2">
+        <v>0</v>
+      </c>
+      <c r="K211" s="2">
         <v>3</v>
       </c>
-      <c r="K211" s="2">
+      <c r="L211" s="2">
         <v>1.5</v>
       </c>
-      <c r="L211" s="2"/>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M211" s="2"/>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
         <v>20</v>
       </c>
@@ -11494,20 +12191,23 @@
         <v>2.5</v>
       </c>
       <c r="H212" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I212" s="2">
         <v>0</v>
       </c>
       <c r="J212" s="2">
+        <v>0</v>
+      </c>
+      <c r="K212" s="2">
         <v>4</v>
       </c>
-      <c r="K212" s="2">
+      <c r="L212" s="2">
         <v>2.5</v>
       </c>
-      <c r="L212" s="2"/>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M212" s="2"/>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
         <v>20</v>
       </c>
@@ -11530,20 +12230,23 @@
         <v>2.5</v>
       </c>
       <c r="H213" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I213" s="2">
         <v>0</v>
       </c>
       <c r="J213" s="2">
+        <v>0</v>
+      </c>
+      <c r="K213" s="2">
         <v>4</v>
       </c>
-      <c r="K213" s="2">
+      <c r="L213" s="2">
         <v>2.5</v>
       </c>
-      <c r="L213" s="2"/>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M213" s="2"/>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
         <v>20</v>
       </c>
@@ -11566,20 +12269,23 @@
         <v>2.5</v>
       </c>
       <c r="H214" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I214" s="2">
         <v>0</v>
       </c>
       <c r="J214" s="2">
+        <v>0</v>
+      </c>
+      <c r="K214" s="2">
         <v>3</v>
       </c>
-      <c r="K214" s="2">
+      <c r="L214" s="2">
         <v>2.5</v>
       </c>
-      <c r="L214" s="2"/>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M214" s="2"/>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
         <v>20</v>
       </c>
@@ -11602,20 +12308,23 @@
         <v>1.5</v>
       </c>
       <c r="H215" s="2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I215" s="2">
         <v>0</v>
       </c>
       <c r="J215" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K215" s="2">
+        <v>2</v>
+      </c>
+      <c r="L215" s="2">
         <v>1.5</v>
       </c>
-      <c r="L215" s="2"/>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M215" s="2"/>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="5" t="s">
         <v>21</v>
       </c>
@@ -11638,20 +12347,23 @@
         <v>4</v>
       </c>
       <c r="H216" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I216" s="2">
         <v>0</v>
       </c>
       <c r="J216" s="2">
+        <v>0</v>
+      </c>
+      <c r="K216" s="2">
         <v>8</v>
       </c>
-      <c r="K216" s="2">
+      <c r="L216" s="2">
         <v>4</v>
       </c>
-      <c r="L216" s="2"/>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M216" s="2"/>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="5" t="s">
         <v>21</v>
       </c>
@@ -11674,20 +12386,23 @@
         <v>3</v>
       </c>
       <c r="H217" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I217" s="2">
         <v>0</v>
       </c>
       <c r="J217" s="2">
+        <v>0</v>
+      </c>
+      <c r="K217" s="2">
         <v>5</v>
       </c>
-      <c r="K217" s="2">
+      <c r="L217" s="2">
         <v>3</v>
       </c>
-      <c r="L217" s="2"/>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M217" s="2"/>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="5" t="s">
         <v>21</v>
       </c>
@@ -11710,20 +12425,23 @@
         <v>10</v>
       </c>
       <c r="H218" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I218" s="2">
         <v>0</v>
       </c>
       <c r="J218" s="2">
+        <v>0</v>
+      </c>
+      <c r="K218" s="2">
         <v>20</v>
       </c>
-      <c r="K218" s="2">
+      <c r="L218" s="2">
         <v>10</v>
       </c>
-      <c r="L218" s="2"/>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M218" s="2"/>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="5" t="s">
         <v>21</v>
       </c>
@@ -11746,20 +12464,23 @@
         <v>4</v>
       </c>
       <c r="H219" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I219" s="2">
         <v>0</v>
       </c>
       <c r="J219" s="2">
+        <v>0</v>
+      </c>
+      <c r="K219" s="2">
         <v>8</v>
       </c>
-      <c r="K219" s="2">
+      <c r="L219" s="2">
         <v>4</v>
       </c>
-      <c r="L219" s="2"/>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M219" s="2"/>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" s="5" t="s">
         <v>21</v>
       </c>
@@ -11782,20 +12503,23 @@
         <v>2.5</v>
       </c>
       <c r="H220" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I220" s="2">
         <v>0</v>
       </c>
       <c r="J220" s="2">
+        <v>0</v>
+      </c>
+      <c r="K220" s="2">
         <v>5</v>
       </c>
-      <c r="K220" s="2">
+      <c r="L220" s="2">
         <v>2.5</v>
       </c>
-      <c r="L220" s="2"/>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M220" s="2"/>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="5" t="s">
         <v>21</v>
       </c>
@@ -11818,20 +12542,23 @@
         <v>2.5</v>
       </c>
       <c r="H221" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I221" s="2">
         <v>0</v>
       </c>
       <c r="J221" s="2">
+        <v>0</v>
+      </c>
+      <c r="K221" s="2">
         <v>5</v>
       </c>
-      <c r="K221" s="2">
+      <c r="L221" s="2">
         <v>2.5</v>
       </c>
-      <c r="L221" s="2"/>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M221" s="2"/>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="5" t="s">
         <v>21</v>
       </c>
@@ -11854,22 +12581,25 @@
         <v>18</v>
       </c>
       <c r="H222" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I222" s="2">
         <v>0</v>
       </c>
       <c r="J222" s="2">
+        <v>0</v>
+      </c>
+      <c r="K222" s="2">
         <v>45</v>
       </c>
-      <c r="K222" s="2">
+      <c r="L222" s="2">
         <v>18</v>
       </c>
-      <c r="L222" s="2" t="s">
+      <c r="M222" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="5" t="s">
         <v>21</v>
       </c>
@@ -11892,20 +12622,23 @@
         <v>4</v>
       </c>
       <c r="H223" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I223" s="2">
         <v>0</v>
       </c>
       <c r="J223" s="2">
+        <v>0</v>
+      </c>
+      <c r="K223" s="2">
         <v>6</v>
       </c>
-      <c r="K223" s="2">
+      <c r="L223" s="2">
         <v>4</v>
       </c>
-      <c r="L223" s="2"/>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M223" s="2"/>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="5" t="s">
         <v>21</v>
       </c>
@@ -11928,20 +12661,23 @@
         <v>4</v>
       </c>
       <c r="H224" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I224" s="2">
         <v>0</v>
       </c>
       <c r="J224" s="2">
+        <v>0</v>
+      </c>
+      <c r="K224" s="2">
         <v>6</v>
       </c>
-      <c r="K224" s="2">
+      <c r="L224" s="2">
         <v>4</v>
       </c>
-      <c r="L224" s="2"/>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M224" s="2"/>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" s="5" t="s">
         <v>21</v>
       </c>
@@ -11964,20 +12700,23 @@
         <v>4</v>
       </c>
       <c r="H225" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I225" s="2">
         <v>0</v>
       </c>
       <c r="J225" s="2">
+        <v>0</v>
+      </c>
+      <c r="K225" s="2">
         <v>6</v>
       </c>
-      <c r="K225" s="2">
+      <c r="L225" s="2">
         <v>4</v>
       </c>
-      <c r="L225" s="2"/>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M225" s="2"/>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" s="5" t="s">
         <v>21</v>
       </c>
@@ -12000,20 +12739,23 @@
         <v>4</v>
       </c>
       <c r="H226" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I226" s="2">
         <v>0</v>
       </c>
       <c r="J226" s="2">
+        <v>0</v>
+      </c>
+      <c r="K226" s="2">
         <v>5</v>
       </c>
-      <c r="K226" s="2">
+      <c r="L226" s="2">
         <v>4</v>
       </c>
-      <c r="L226" s="2"/>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M226" s="2"/>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" s="5" t="s">
         <v>21</v>
       </c>
@@ -12036,20 +12778,23 @@
         <v>2.5</v>
       </c>
       <c r="H227" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I227" s="2">
         <v>0</v>
       </c>
       <c r="J227" s="2">
+        <v>0</v>
+      </c>
+      <c r="K227" s="2">
         <v>3</v>
       </c>
-      <c r="K227" s="2">
+      <c r="L227" s="2">
         <v>2.5</v>
       </c>
-      <c r="L227" s="2"/>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M227" s="2"/>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" s="5" t="s">
         <v>22</v>
       </c>
@@ -12072,20 +12817,23 @@
         <v>7</v>
       </c>
       <c r="H228" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I228" s="2">
         <v>0</v>
       </c>
       <c r="J228" s="2">
+        <v>0</v>
+      </c>
+      <c r="K228" s="2">
         <v>10</v>
       </c>
-      <c r="K228" s="2">
+      <c r="L228" s="2">
         <v>7</v>
       </c>
-      <c r="L228" s="2"/>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M228" s="2"/>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>22</v>
       </c>
@@ -12108,20 +12856,23 @@
         <v>8</v>
       </c>
       <c r="H229" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I229" s="2">
         <v>0</v>
       </c>
       <c r="J229" s="2">
+        <v>0</v>
+      </c>
+      <c r="K229" s="2">
         <v>15</v>
       </c>
-      <c r="K229" s="2">
+      <c r="L229" s="2">
         <v>8</v>
       </c>
-      <c r="L229" s="2"/>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M229" s="2"/>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>22</v>
       </c>
@@ -12144,20 +12895,23 @@
         <v>7</v>
       </c>
       <c r="H230" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I230" s="2">
         <v>0</v>
       </c>
       <c r="J230" s="2">
+        <v>0</v>
+      </c>
+      <c r="K230" s="2">
         <v>8</v>
       </c>
-      <c r="K230" s="2">
+      <c r="L230" s="2">
         <v>7</v>
       </c>
-      <c r="L230" s="2"/>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M230" s="2"/>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>22</v>
       </c>
@@ -12180,20 +12934,23 @@
         <v>4</v>
       </c>
       <c r="H231" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I231" s="2">
         <v>0</v>
       </c>
       <c r="J231" s="2">
+        <v>0</v>
+      </c>
+      <c r="K231" s="2">
         <v>6</v>
       </c>
-      <c r="K231" s="2">
+      <c r="L231" s="2">
         <v>4</v>
       </c>
-      <c r="L231" s="2"/>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M231" s="2"/>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>22</v>
       </c>
@@ -12216,21 +12973,24 @@
         <v>3</v>
       </c>
       <c r="H232" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I232" s="2">
         <v>0</v>
       </c>
       <c r="J232" s="2">
+        <v>0</v>
+      </c>
+      <c r="K232" s="2">
         <v>4</v>
       </c>
-      <c r="K232" s="2">
+      <c r="L232" s="2">
         <v>3</v>
       </c>
-      <c r="L232" s="2"/>
+      <c r="M232" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L232"/>
+  <autoFilter ref="A1:M232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>

--- a/docs/estimation/SVT_transformation_effort_estimate.xlsx
+++ b/docs/estimation/SVT_transformation_effort_estimate.xlsx
@@ -23,24 +23,18 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Нормы_и_допущения!$A$1:$C$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Подзадачи!$A$1:$M$232</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Сделано_vs_Остаток!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Этапы!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Этапы!$A$1:$K$16</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="485">
   <si>
     <t>Этап</t>
   </si>
   <si>
-    <t>Полная_без_агента_чел_дни</t>
-  </si>
-  <si>
-    <t>Полная_с_агентом_чел_дни</t>
-  </si>
-  <si>
     <t>Сделано_без_агента</t>
   </si>
   <si>
@@ -320,12 +314,6 @@
     <t>Задача_бэклога</t>
   </si>
   <si>
-    <t>Полная_без_агента</t>
-  </si>
-  <si>
-    <t>Полная_с_агентом</t>
-  </si>
-  <si>
     <t>§0.1</t>
   </si>
   <si>
@@ -1490,14 +1478,20 @@
     <t>Задача</t>
   </si>
   <si>
-    <t>Без агента, ч.д</t>
+    <t>оценка ИИ с ИИ</t>
+  </si>
+  <si>
+    <t>Оценка человека с ИИ</t>
+  </si>
+  <si>
+    <t>оценка ИИ без ИИ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1533,13 +1527,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="5"/>
@@ -1557,6 +1544,27 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1612,7 +1620,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1630,10 +1638,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1937,536 +1947,629 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12">
+        <f>SUM(Подзадачи!F2:F20)</f>
+        <v>46</v>
+      </c>
+      <c r="C2" s="10">
+        <f>SUM(Подзадачи!G2:G20)</f>
+        <v>29</v>
+      </c>
+      <c r="D2" s="13">
+        <f>SUM(Подзадачи!H2:H20)</f>
+        <v>23.5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>39.4</v>
+      </c>
+      <c r="F2" s="2">
+        <v>24.2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="I2" s="2">
+        <v>37</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B3" s="12">
+        <f>SUM(Подзадачи!F21:F68)</f>
+        <v>149</v>
+      </c>
+      <c r="C3" s="10">
+        <f>SUM(Подзадачи!G21:G68)</f>
+        <v>90.4</v>
+      </c>
+      <c r="D3" s="13">
+        <f>SUM(Подзадачи!H21:H68)</f>
+        <v>58.5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>127.2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="G3" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="H3" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="I3" s="2">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="9">
-        <v>46</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B4" s="12">
+        <f>SUM(Подзадачи!F69:F85)</f>
+        <v>373</v>
+      </c>
+      <c r="C4" s="10">
+        <f>SUM(Подзадачи!G69:G85)</f>
+        <v>140.5</v>
+      </c>
+      <c r="D4" s="13">
+        <f>SUM(Подзадачи!H69:H85)</f>
+        <v>70.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>27.8</v>
+      </c>
+      <c r="F4" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>345.2</v>
+      </c>
+      <c r="H4" s="2">
+        <v>128.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>62.3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12">
+        <f>SUM(Подзадачи!F86:F91)</f>
+        <v>61</v>
+      </c>
+      <c r="C5" s="10">
+        <f>SUM(Подзадачи!G86:G91)</f>
+        <v>28.5</v>
+      </c>
+      <c r="D5" s="13">
+        <f>SUM(Подзадачи!H86:H91)</f>
+        <v>21.5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>61</v>
+      </c>
+      <c r="H5" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>53.3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="12">
+        <f>SUM(Подзадачи!F92:F98)</f>
+        <v>35</v>
+      </c>
+      <c r="C6" s="10">
+        <f>SUM(Подзадачи!G92:G98)</f>
+        <v>19.5</v>
+      </c>
+      <c r="D6" s="13">
+        <f>SUM(Подзадачи!H92:H98)</f>
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>44.3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="12">
+        <f>SUM(Подзадачи!F99:F127)</f>
+        <v>116.5</v>
+      </c>
+      <c r="C7" s="10">
+        <f>SUM(Подзадачи!G99:G127)</f>
+        <v>70.5</v>
+      </c>
+      <c r="D7" s="13">
+        <f>SUM(Подзадачи!H99:H127)</f>
+        <v>56.5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>116.5</v>
+      </c>
+      <c r="H7" s="2">
+        <v>70.5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="12">
+        <f>SUM(Подзадачи!F128:F142)</f>
+        <v>547.5</v>
+      </c>
+      <c r="C8" s="10">
+        <f>SUM(Подзадачи!G128:G142)</f>
+        <v>246.3</v>
+      </c>
+      <c r="D8" s="13">
+        <f>SUM(Подзадачи!H128:H142)</f>
+        <v>111</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>547.5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>246.3</v>
+      </c>
+      <c r="I8" s="2">
+        <v>55</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(Подзадачи!F143:F167)</f>
+        <v>64</v>
+      </c>
+      <c r="C9" s="10">
+        <f>SUM(Подзадачи!G143:G167)</f>
+        <v>40.900000000000006</v>
+      </c>
+      <c r="D9" s="13">
+        <f>SUM(Подзадачи!H143:H167)</f>
+        <v>32</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G9" s="2">
+        <v>59.4</v>
+      </c>
+      <c r="H9" s="2">
+        <v>38.6</v>
+      </c>
+      <c r="I9" s="2">
+        <v>36.1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="12">
+        <f>SUM(Подзадачи!F168:F181)</f>
+        <v>228.5</v>
+      </c>
+      <c r="C10" s="10">
+        <f>SUM(Подзадачи!G168:G181)</f>
+        <v>100.30000000000001</v>
+      </c>
+      <c r="D10" s="13">
+        <f>SUM(Подзадачи!H168:H181)</f>
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>228.5</v>
+      </c>
+      <c r="H10" s="2">
+        <v>100.3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>56.1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.04</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="12">
+        <f>SUM(Подзадачи!F182:F192)</f>
+        <v>66</v>
+      </c>
+      <c r="C11" s="10">
+        <f>SUM(Подзадачи!G182:G192)</f>
+        <v>37</v>
+      </c>
+      <c r="D11" s="13">
+        <f>SUM(Подзадачи!H182:H192)</f>
+        <v>33.5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2">
+        <v>37</v>
+      </c>
+      <c r="I11" s="2">
+        <v>43.9</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="12">
+        <f>SUM(Подзадачи!F193:F203)</f>
+        <v>37.5</v>
+      </c>
+      <c r="C12" s="10">
+        <f>SUM(Подзадачи!G193:G203)</f>
+        <v>21.8</v>
+      </c>
+      <c r="D12" s="13">
+        <f>SUM(Подзадачи!H193:H203)</f>
+        <v>18</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="H12" s="2">
+        <v>21.8</v>
+      </c>
+      <c r="I12" s="2">
+        <v>41.9</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="12">
+        <f>SUM(Подзадачи!F204:F215)</f>
+        <v>86</v>
+      </c>
+      <c r="C13" s="10">
+        <f>SUM(Подзадачи!G204:G215)</f>
+        <v>42</v>
+      </c>
+      <c r="D13" s="13">
+        <f>SUM(Подзадачи!H204:H215)</f>
+        <v>38.5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>86</v>
+      </c>
+      <c r="H13" s="2">
+        <v>42</v>
+      </c>
+      <c r="I13" s="2">
+        <v>51.2</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="12">
+        <f>SUM(Подзадачи!F216:F227)</f>
+        <v>122</v>
+      </c>
+      <c r="C14" s="10">
+        <f>SUM(Подзадачи!G216:G227)</f>
+        <v>62.5</v>
+      </c>
+      <c r="D14" s="13">
+        <f>SUM(Подзадачи!H216:H227)</f>
+        <v>55</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>122</v>
+      </c>
+      <c r="H14" s="2">
+        <v>62.5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>48.8</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="12">
+        <f>SUM(Подзадачи!F228:F232)</f>
+        <v>43</v>
+      </c>
+      <c r="C15" s="10">
+        <f>SUM(Подзадачи!G228:G232)</f>
         <v>29</v>
       </c>
-      <c r="D2" s="2">
-        <v>39.4</v>
-      </c>
-      <c r="E2" s="2">
-        <v>24.2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="G2" s="2">
-        <v>4.8</v>
-      </c>
-      <c r="H2" s="2">
-        <v>37</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="D15" s="13">
+        <f>SUM(Подзадачи!H228:H232)</f>
+        <v>26</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>43</v>
+      </c>
+      <c r="H15" s="2">
+        <v>29</v>
+      </c>
+      <c r="I15" s="2">
+        <v>32.6</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="2">
         <v>0.13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="9">
-        <v>149</v>
-      </c>
-      <c r="C3" s="11">
-        <v>90.4</v>
-      </c>
-      <c r="D3" s="2">
-        <v>127.2</v>
-      </c>
-      <c r="E3" s="2">
-        <v>73.900000000000006</v>
-      </c>
-      <c r="F3" s="2">
-        <v>21.9</v>
-      </c>
-      <c r="G3" s="2">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="H3" s="2">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="9">
-        <v>373</v>
-      </c>
-      <c r="C4" s="11">
-        <v>140.5</v>
-      </c>
-      <c r="D4" s="2">
-        <v>27.8</v>
-      </c>
-      <c r="E4" s="2">
-        <v>12.4</v>
-      </c>
-      <c r="F4" s="2">
-        <v>345.2</v>
-      </c>
-      <c r="G4" s="2">
-        <v>128.1</v>
-      </c>
-      <c r="H4" s="2">
-        <v>62.3</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1.7</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="9">
-        <v>61</v>
-      </c>
-      <c r="C5" s="11">
-        <v>28.5</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>61</v>
-      </c>
-      <c r="G5" s="2">
-        <v>28.5</v>
-      </c>
-      <c r="H5" s="2">
-        <v>53.3</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="9">
-        <v>35</v>
-      </c>
-      <c r="C6" s="11">
-        <v>19.5</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>35</v>
-      </c>
-      <c r="G6" s="2">
-        <v>19.5</v>
-      </c>
-      <c r="H6" s="2">
-        <v>44.3</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="9">
-        <v>116.5</v>
-      </c>
-      <c r="C7" s="11">
-        <v>70.5</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>116.5</v>
-      </c>
-      <c r="G7" s="2">
-        <v>70.5</v>
-      </c>
-      <c r="H7" s="2">
-        <v>39.5</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.53</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="9">
-        <v>547.5</v>
-      </c>
-      <c r="C8" s="11">
-        <v>246.3</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>547.5</v>
-      </c>
-      <c r="G8" s="2">
-        <v>246.3</v>
-      </c>
-      <c r="H8" s="2">
-        <v>55</v>
-      </c>
-      <c r="I8" s="2">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="9">
-        <v>64</v>
-      </c>
-      <c r="C9" s="11">
-        <v>40.9</v>
-      </c>
-      <c r="D9" s="2">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F9" s="2">
-        <v>59.4</v>
-      </c>
-      <c r="G9" s="2">
-        <v>38.6</v>
-      </c>
-      <c r="H9" s="2">
-        <v>36.1</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="9">
-        <v>228.5</v>
-      </c>
-      <c r="C10" s="11">
-        <v>100.3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>228.5</v>
-      </c>
-      <c r="G10" s="2">
-        <v>100.3</v>
-      </c>
-      <c r="H10" s="2">
-        <v>56.1</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1.04</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="9">
-        <v>66</v>
-      </c>
-      <c r="C11" s="11">
-        <v>37</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>66</v>
-      </c>
-      <c r="G11" s="2">
-        <v>37</v>
-      </c>
-      <c r="H11" s="2">
-        <v>43.9</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="9">
-        <v>37.5</v>
-      </c>
-      <c r="C12" s="11">
-        <v>21.8</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>37.5</v>
-      </c>
-      <c r="G12" s="2">
-        <v>21.8</v>
-      </c>
-      <c r="H12" s="2">
-        <v>41.9</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="9">
-        <v>86</v>
-      </c>
-      <c r="C13" s="11">
-        <v>42</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>86</v>
-      </c>
-      <c r="G13" s="2">
-        <v>42</v>
-      </c>
-      <c r="H13" s="2">
-        <v>51.2</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0.39</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="9">
-        <v>122</v>
-      </c>
-      <c r="C14" s="11">
-        <v>62.5</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>122</v>
-      </c>
-      <c r="G14" s="2">
-        <v>62.5</v>
-      </c>
-      <c r="H14" s="2">
-        <v>48.8</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="9">
-        <v>43</v>
-      </c>
-      <c r="C15" s="11">
-        <v>29</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>43</v>
-      </c>
-      <c r="G15" s="2">
-        <v>29</v>
-      </c>
-      <c r="H15" s="2">
-        <v>32.6</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>1975</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>958.2</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="14">
+        <f>SUM(D2:D15)</f>
+        <v>629.5</v>
+      </c>
+      <c r="E16" s="3">
         <v>199</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="3">
         <v>112.8</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>1776.1</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>845.3</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>51.5</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
         <v>8.98</v>
       </c>
-      <c r="J16" s="3">
+      <c r="K16" s="3">
         <v>4.3600000000000003</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J16"/>
+  <autoFilter ref="A1:K16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2479,7 +2582,7 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="5" max="5" width="25.21875" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
@@ -2491,28 +2594,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>484</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>482</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>483</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2520,10 +2623,11 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="2">
-        <v>8.5</v>
+        <v>94</v>
+      </c>
+      <c r="C2" s="2" t="e">
+        <f ca="1">сумм(Подзадачи!F2:F5)</f>
+        <v>#NAME?</v>
       </c>
       <c r="D2" s="2">
         <v>5.5</v>
@@ -2549,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C3" s="2">
         <v>4.5</v>
@@ -2578,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2">
         <v>12</v>
@@ -2607,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2">
         <v>8</v>
@@ -2636,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2">
         <v>13</v>
@@ -2662,10 +2766,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2">
         <v>7</v>
@@ -2691,10 +2795,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2">
         <v>10</v>
@@ -2720,10 +2824,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2">
         <v>17</v>
@@ -2749,10 +2853,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>16</v>
@@ -2778,10 +2882,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>12</v>
@@ -2807,10 +2911,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C12" s="2">
         <v>6.5</v>
@@ -2836,10 +2940,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C13" s="2">
         <v>8</v>
@@ -2865,10 +2969,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C14" s="2">
         <v>6</v>
@@ -2894,10 +2998,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
@@ -2923,10 +3027,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C16" s="2">
         <v>27</v>
@@ -2952,10 +3056,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2">
         <v>21</v>
@@ -2981,10 +3085,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2">
         <v>18.5</v>
@@ -3010,10 +3114,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C19" s="2">
         <v>7</v>
@@ -3039,10 +3143,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C20" s="2">
         <v>293</v>
@@ -3068,10 +3172,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C21" s="2">
         <v>15</v>
@@ -3097,10 +3201,10 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C22" s="2">
         <v>58</v>
@@ -3126,10 +3230,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C23" s="2">
         <v>61</v>
@@ -3155,10 +3259,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C24" s="2">
         <v>35</v>
@@ -3184,10 +3288,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C25" s="2">
         <v>26.5</v>
@@ -3213,10 +3317,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C26" s="2">
         <v>13</v>
@@ -3242,10 +3346,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C27" s="2">
         <v>13</v>
@@ -3271,10 +3375,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C28" s="2">
         <v>23</v>
@@ -3300,10 +3404,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -3329,10 +3433,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C30" s="2">
         <v>41</v>
@@ -3358,10 +3462,10 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C31" s="2">
         <v>9.5</v>
@@ -3387,10 +3491,10 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C32" s="2">
         <v>466</v>
@@ -3416,10 +3520,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C33" s="2">
         <v>20</v>
@@ -3445,10 +3549,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C34" s="2">
         <v>52</v>
@@ -3474,10 +3578,10 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C35" s="2">
         <v>8</v>
@@ -3503,10 +3607,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C36" s="2">
         <v>16</v>
@@ -3532,10 +3636,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C37" s="2">
         <v>16</v>
@@ -3561,10 +3665,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -3590,10 +3694,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C39" s="2">
         <v>24</v>
@@ -3619,10 +3723,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C40" s="2">
         <v>5</v>
@@ -3648,10 +3752,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C41" s="2">
         <v>172.5</v>
@@ -3677,10 +3781,10 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C42" s="2">
         <v>12</v>
@@ -3706,10 +3810,10 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C43" s="2">
         <v>39</v>
@@ -3735,10 +3839,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C44" s="2">
         <v>66</v>
@@ -3764,10 +3868,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C45" s="2">
         <v>37.5</v>
@@ -3793,10 +3897,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C46" s="2">
         <v>86</v>
@@ -3822,10 +3926,10 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C47" s="2">
         <v>122</v>
@@ -3851,10 +3955,10 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C48" s="2">
         <v>43</v>
@@ -3894,8 +3998,9 @@
     <col min="3" max="3" width="14" style="6" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="8" width="26" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
@@ -3903,45 +4008,45 @@
     <col min="13" max="13" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
+      <c r="G1" s="8" t="s">
+        <v>482</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>2</v>
+        <v>483</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -3949,16 +4054,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F2" s="2">
         <v>1.5</v>
@@ -3988,16 +4093,16 @@
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F3" s="2">
         <v>3</v>
@@ -4027,16 +4132,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -4066,16 +4171,16 @@
         <v>0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
@@ -4084,7 +4189,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2">
         <v>3</v>
@@ -4105,16 +4210,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -4144,16 +4249,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
@@ -4183,16 +4288,16 @@
         <v>0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F8" s="2">
         <v>1.5</v>
@@ -4222,16 +4327,16 @@
         <v>0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F9" s="2">
         <v>4</v>
@@ -4240,7 +4345,7 @@
         <v>2.5</v>
       </c>
       <c r="H9" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
@@ -4261,16 +4366,16 @@
         <v>0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
@@ -4279,7 +4384,7 @@
         <v>3.5</v>
       </c>
       <c r="H10" s="2">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I10" s="2">
         <v>6</v>
@@ -4300,16 +4405,16 @@
         <v>0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F11" s="2">
         <v>2</v>
@@ -4339,16 +4444,16 @@
         <v>0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F12" s="2">
         <v>4</v>
@@ -4357,7 +4462,7 @@
         <v>2.5</v>
       </c>
       <c r="H12" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I12" s="2">
         <v>4</v>
@@ -4378,16 +4483,16 @@
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
@@ -4411,7 +4516,7 @@
         <v>0.3</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -4419,16 +4524,16 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F14" s="2">
         <v>2</v>
@@ -4458,16 +4563,16 @@
         <v>0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F15" s="2">
         <v>3</v>
@@ -4476,7 +4581,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2">
         <v>3</v>
@@ -4497,16 +4602,16 @@
         <v>0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
@@ -4536,16 +4641,16 @@
         <v>0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F17" s="2">
         <v>2</v>
@@ -4554,7 +4659,7 @@
         <v>1.5</v>
       </c>
       <c r="H17" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="2">
         <v>2</v>
@@ -4575,16 +4680,16 @@
         <v>0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F18" s="2">
         <v>2</v>
@@ -4593,7 +4698,7 @@
         <v>1.5</v>
       </c>
       <c r="H18" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2">
         <v>2</v>
@@ -4614,16 +4719,16 @@
         <v>0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F19" s="2">
         <v>3</v>
@@ -4632,7 +4737,7 @@
         <v>2.5</v>
       </c>
       <c r="H19" s="2">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
@@ -4653,16 +4758,16 @@
         <v>0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
@@ -4689,19 +4794,19 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F21" s="2">
         <v>2</v>
@@ -4710,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I21" s="2">
         <v>2</v>
@@ -4728,19 +4833,19 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F22" s="2">
         <v>2</v>
@@ -4749,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I22" s="2">
         <v>2</v>
@@ -4767,19 +4872,19 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F23" s="2">
         <v>1.5</v>
@@ -4788,7 +4893,7 @@
         <v>0.8</v>
       </c>
       <c r="H23" s="2">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I23" s="2">
         <v>1.5</v>
@@ -4806,19 +4911,19 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F24" s="2">
         <v>1.5</v>
@@ -4827,7 +4932,7 @@
         <v>0.8</v>
       </c>
       <c r="H24" s="2">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I24" s="2">
         <v>1.5</v>
@@ -4845,19 +4950,19 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F25" s="2">
         <v>3</v>
@@ -4866,7 +4971,7 @@
         <v>1.5</v>
       </c>
       <c r="H25" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I25" s="2">
         <v>3</v>
@@ -4884,19 +4989,19 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F26" s="2">
         <v>1.5</v>
@@ -4905,7 +5010,7 @@
         <v>0.8</v>
       </c>
       <c r="H26" s="2">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="I26" s="2">
         <v>1.5</v>
@@ -4923,19 +5028,19 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F27" s="2">
         <v>2.5</v>
@@ -4944,7 +5049,7 @@
         <v>1.2</v>
       </c>
       <c r="H27" s="2">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="I27" s="2">
         <v>2.5</v>
@@ -4962,19 +5067,19 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F28" s="2">
         <v>3</v>
@@ -4983,7 +5088,7 @@
         <v>1.5</v>
       </c>
       <c r="H28" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I28" s="2">
         <v>3</v>
@@ -5001,19 +5106,19 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F29" s="2">
         <v>8</v>
@@ -5040,19 +5145,19 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F30" s="2">
         <v>4</v>
@@ -5079,19 +5184,19 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F31" s="2">
         <v>5</v>
@@ -5100,7 +5205,7 @@
         <v>2.5</v>
       </c>
       <c r="H31" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I31" s="2">
         <v>5</v>
@@ -5118,19 +5223,19 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C32" s="5">
         <v>2.1</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F32" s="2">
         <v>3</v>
@@ -5139,7 +5244,7 @@
         <v>2</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="2">
         <v>3</v>
@@ -5157,19 +5262,19 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C33" s="5">
         <v>2.2000000000000002</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F33" s="2">
         <v>2</v>
@@ -5178,7 +5283,7 @@
         <v>1.5</v>
       </c>
       <c r="H33" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I33" s="2">
         <v>2</v>
@@ -5196,19 +5301,19 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C34" s="5">
         <v>2.2999999999999998</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F34" s="2">
         <v>4</v>
@@ -5235,19 +5340,19 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C35" s="5">
         <v>2.4</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F35" s="2">
         <v>2</v>
@@ -5256,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
@@ -5274,19 +5379,19 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C36" s="5">
         <v>2.5</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F36" s="2">
         <v>5</v>
@@ -5313,19 +5418,19 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F37" s="2">
         <v>2</v>
@@ -5352,19 +5457,19 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F38" s="2">
         <v>4</v>
@@ -5373,7 +5478,7 @@
         <v>2.5</v>
       </c>
       <c r="H38" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I38" s="2">
         <v>4</v>
@@ -5391,19 +5496,19 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F39" s="2">
         <v>6</v>
@@ -5412,7 +5517,7 @@
         <v>3.5</v>
       </c>
       <c r="H39" s="2">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I39" s="2">
         <v>6</v>
@@ -5430,19 +5535,19 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F40" s="2">
         <v>4</v>
@@ -5451,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40" s="2">
         <v>4</v>
@@ -5469,19 +5574,19 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F41" s="2">
         <v>2.5</v>
@@ -5490,7 +5595,7 @@
         <v>1.2</v>
       </c>
       <c r="H41" s="2">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="2">
         <v>2.5</v>
@@ -5508,19 +5613,19 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F42" s="2">
         <v>4</v>
@@ -5547,19 +5652,19 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F43" s="2">
         <v>2.5</v>
@@ -5568,7 +5673,7 @@
         <v>1.2</v>
       </c>
       <c r="H43" s="2">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="I43" s="2">
         <v>2.5</v>
@@ -5586,19 +5691,19 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F44" s="2">
         <v>1.5</v>
@@ -5625,19 +5730,19 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F45" s="2">
         <v>1.5</v>
@@ -5646,7 +5751,7 @@
         <v>0.8</v>
       </c>
       <c r="H45" s="2">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I45" s="2">
         <v>1.5</v>
@@ -5664,19 +5769,19 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F46" s="2">
         <v>1.5</v>
@@ -5685,7 +5790,7 @@
         <v>0.8</v>
       </c>
       <c r="H46" s="2">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I46" s="2">
         <v>1.5</v>
@@ -5703,19 +5808,19 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2">
         <v>2</v>
@@ -5724,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I47" s="2">
         <v>2</v>
@@ -5742,19 +5847,19 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -5763,7 +5868,7 @@
         <v>0.8</v>
       </c>
       <c r="H48" s="2">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
@@ -5781,19 +5886,19 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -5802,7 +5907,7 @@
         <v>2.5</v>
       </c>
       <c r="H49" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I49" s="2">
         <v>0</v>
@@ -5817,24 +5922,24 @@
         <v>0</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
@@ -5843,7 +5948,7 @@
         <v>2.5</v>
       </c>
       <c r="H50" s="2">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2">
         <v>0</v>
@@ -5858,24 +5963,24 @@
         <v>0</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C51" s="5">
         <v>4.0999999999999996</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
@@ -5902,19 +6007,19 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C52" s="5">
         <v>4.2</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F52" s="2">
         <v>12</v>
@@ -5923,7 +6028,7 @@
         <v>5</v>
       </c>
       <c r="H52" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I52" s="2">
         <v>12</v>
@@ -5938,24 +6043,24 @@
         <v>0</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C53" s="5">
         <v>4.3</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F53" s="2">
         <v>5</v>
@@ -5964,7 +6069,7 @@
         <v>3</v>
       </c>
       <c r="H53" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I53" s="2">
         <v>5</v>
@@ -5982,19 +6087,19 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C54" s="5">
         <v>4.4000000000000004</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F54" s="2">
         <v>4</v>
@@ -6003,7 +6108,7 @@
         <v>2.5</v>
       </c>
       <c r="H54" s="2">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I54" s="2">
         <v>4</v>
@@ -6021,19 +6126,19 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C55" s="5">
         <v>4.5</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F55" s="2">
         <v>2</v>
@@ -6042,7 +6147,7 @@
         <v>1.5</v>
       </c>
       <c r="H55" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I55" s="2">
         <v>2</v>
@@ -6060,19 +6165,19 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C56" s="5">
         <v>4.5999999999999996</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F56" s="2">
         <v>2</v>
@@ -6099,19 +6204,19 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C57" s="5">
         <v>5.0999999999999996</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F57" s="2">
         <v>2</v>
@@ -6120,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I57" s="2">
         <v>2</v>
@@ -6138,19 +6243,19 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C58" s="5">
         <v>5.2</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F58" s="2">
         <v>4</v>
@@ -6159,7 +6264,7 @@
         <v>2.5</v>
       </c>
       <c r="H58" s="2">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="I58" s="2">
         <v>4</v>
@@ -6177,19 +6282,19 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C59" s="5">
         <v>5.3</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F59" s="2">
         <v>12</v>
@@ -6198,7 +6303,7 @@
         <v>6</v>
       </c>
       <c r="H59" s="2">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="I59" s="2">
         <v>12</v>
@@ -6213,24 +6318,24 @@
         <v>0</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C60" s="5">
         <v>5.4</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F60" s="2">
         <v>3</v>
@@ -6239,7 +6344,7 @@
         <v>2</v>
       </c>
       <c r="H60" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="2">
         <v>1.8</v>
@@ -6254,24 +6359,24 @@
         <v>0.8</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C61" s="5">
         <v>6.1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F61" s="2">
         <v>1</v>
@@ -6298,19 +6403,19 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C62" s="5">
         <v>6.2</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F62" s="2">
         <v>3</v>
@@ -6319,7 +6424,7 @@
         <v>1.5</v>
       </c>
       <c r="H62" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I62" s="2">
         <v>3</v>
@@ -6337,19 +6442,19 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C63" s="5">
         <v>6.3</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F63" s="2">
         <v>1.5</v>
@@ -6373,24 +6478,24 @@
         <v>0.7</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C64" s="5">
         <v>6.4</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F64" s="2">
         <v>2</v>
@@ -6399,7 +6504,7 @@
         <v>1.5</v>
       </c>
       <c r="H64" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I64" s="2">
         <v>2</v>
@@ -6417,19 +6522,19 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C65" s="5">
         <v>6.5</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F65" s="2">
         <v>3</v>
@@ -6438,7 +6543,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="2">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I65" s="2">
         <v>3</v>
@@ -6456,19 +6561,19 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C66" s="5">
         <v>6.6</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F66" s="2">
         <v>2</v>
@@ -6477,7 +6582,7 @@
         <v>1.5</v>
       </c>
       <c r="H66" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I66" s="2">
         <v>1.4</v>
@@ -6495,19 +6600,19 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C67" s="5">
         <v>6.7</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F67" s="2">
         <v>2</v>
@@ -6534,19 +6639,19 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C68" s="5">
         <v>6.8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F68" s="2">
         <v>4</v>
@@ -6555,7 +6660,7 @@
         <v>3.5</v>
       </c>
       <c r="H68" s="2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I68" s="2">
         <v>0</v>
@@ -6573,19 +6678,19 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F69" s="2">
         <v>2</v>
@@ -6612,19 +6717,19 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F70" s="2">
         <v>3</v>
@@ -6633,7 +6738,7 @@
         <v>1.5</v>
       </c>
       <c r="H70" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I70" s="2">
         <v>0</v>
@@ -6651,19 +6756,19 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F71" s="2">
         <v>2</v>
@@ -6672,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I71" s="2">
         <v>0.8</v>
@@ -6687,24 +6792,24 @@
         <v>0.6</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F72" s="2">
         <v>54</v>
@@ -6713,7 +6818,7 @@
         <v>16.5</v>
       </c>
       <c r="H72" s="2">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="I72" s="2">
         <v>18</v>
@@ -6728,24 +6833,24 @@
         <v>11</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F73" s="2">
         <v>28</v>
@@ -6754,7 +6859,7 @@
         <v>8.5</v>
       </c>
       <c r="H73" s="2">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="I73" s="2">
         <v>0</v>
@@ -6772,19 +6877,19 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F74" s="2">
         <v>41</v>
@@ -6793,7 +6898,7 @@
         <v>12.5</v>
       </c>
       <c r="H74" s="2">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="I74" s="2">
         <v>5</v>
@@ -6808,24 +6913,24 @@
         <v>11</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F75" s="2">
         <v>28</v>
@@ -6834,7 +6939,7 @@
         <v>8.5</v>
       </c>
       <c r="H75" s="2">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="I75" s="2">
         <v>0</v>
@@ -6852,19 +6957,19 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F76" s="2">
         <v>28</v>
@@ -6873,7 +6978,7 @@
         <v>8.5</v>
       </c>
       <c r="H76" s="2">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="I76" s="2">
         <v>0</v>
@@ -6891,19 +6996,19 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F77" s="2">
         <v>114</v>
@@ -6912,7 +7017,7 @@
         <v>33</v>
       </c>
       <c r="H77" s="2">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I77" s="2">
         <v>0</v>
@@ -6930,19 +7035,19 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F78" s="2">
         <v>15</v>
@@ -6951,7 +7056,7 @@
         <v>12</v>
       </c>
       <c r="H78" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I78" s="2">
         <v>4</v>
@@ -6966,24 +7071,24 @@
         <v>7</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F79" s="2">
         <v>10</v>
@@ -7010,19 +7115,19 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F80" s="2">
         <v>12</v>
@@ -7031,7 +7136,7 @@
         <v>7</v>
       </c>
       <c r="H80" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I80" s="2">
         <v>0</v>
@@ -7049,19 +7154,19 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F81" s="2">
         <v>8</v>
@@ -7070,7 +7175,7 @@
         <v>5</v>
       </c>
       <c r="H81" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I81" s="2">
         <v>0</v>
@@ -7088,19 +7193,19 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F82" s="2">
         <v>8</v>
@@ -7127,19 +7232,19 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F83" s="2">
         <v>10</v>
@@ -7148,7 +7253,7 @@
         <v>6</v>
       </c>
       <c r="H83" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I83" s="2">
         <v>0</v>
@@ -7166,19 +7271,19 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F84" s="2">
         <v>6</v>
@@ -7205,19 +7310,19 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F85" s="2">
         <v>4</v>
@@ -7226,7 +7331,7 @@
         <v>3.5</v>
       </c>
       <c r="H85" s="2">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I85" s="2">
         <v>0</v>
@@ -7244,19 +7349,19 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C86" s="5">
         <v>8.1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F86" s="2">
         <v>5</v>
@@ -7283,19 +7388,19 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C87" s="5">
         <v>8.1999999999999993</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F87" s="2">
         <v>4</v>
@@ -7322,19 +7427,19 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C88" s="5">
         <v>8.3000000000000007</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F88" s="2">
         <v>5</v>
@@ -7343,7 +7448,7 @@
         <v>2.5</v>
       </c>
       <c r="H88" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I88" s="2">
         <v>0</v>
@@ -7361,19 +7466,19 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C89" s="5">
         <v>8.4</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F89" s="2">
         <v>40</v>
@@ -7382,7 +7487,7 @@
         <v>16</v>
       </c>
       <c r="H89" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I89" s="2">
         <v>0</v>
@@ -7397,24 +7502,24 @@
         <v>16</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C90" s="5">
         <v>8.5</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F90" s="2">
         <v>4</v>
@@ -7423,7 +7528,7 @@
         <v>2.5</v>
       </c>
       <c r="H90" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I90" s="2">
         <v>0</v>
@@ -7441,19 +7546,19 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C91" s="5">
         <v>8.6</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F91" s="2">
         <v>3</v>
@@ -7480,19 +7585,19 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C92" s="5">
         <v>9.1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F92" s="2">
         <v>5</v>
@@ -7519,19 +7624,19 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C93" s="5">
         <v>9.1999999999999993</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F93" s="2">
         <v>8</v>
@@ -7540,7 +7645,7 @@
         <v>4</v>
       </c>
       <c r="H93" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I93" s="2">
         <v>0</v>
@@ -7558,19 +7663,19 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C94" s="5">
         <v>9.3000000000000007</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F94" s="2">
         <v>8</v>
@@ -7579,7 +7684,7 @@
         <v>4</v>
       </c>
       <c r="H94" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I94" s="2">
         <v>0</v>
@@ -7597,19 +7702,19 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C95" s="5">
         <v>9.4</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F95" s="2">
         <v>6</v>
@@ -7618,7 +7723,7 @@
         <v>3</v>
       </c>
       <c r="H95" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I95" s="2">
         <v>0</v>
@@ -7636,19 +7741,19 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C96" s="5">
         <v>9.5</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F96" s="2">
         <v>3</v>
@@ -7657,7 +7762,7 @@
         <v>1.5</v>
       </c>
       <c r="H96" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I96" s="2">
         <v>0</v>
@@ -7675,19 +7780,19 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C97" s="5">
         <v>9.6</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F97" s="2">
         <v>3</v>
@@ -7714,19 +7819,19 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C98" s="5">
         <v>9.6999999999999993</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F98" s="2">
         <v>2</v>
@@ -7753,19 +7858,19 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F99" s="2">
         <v>4</v>
@@ -7774,7 +7879,7 @@
         <v>2.5</v>
       </c>
       <c r="H99" s="2">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I99" s="2">
         <v>0</v>
@@ -7792,19 +7897,19 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F100" s="2">
         <v>12</v>
@@ -7813,7 +7918,7 @@
         <v>6</v>
       </c>
       <c r="H100" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I100" s="2">
         <v>0</v>
@@ -7831,19 +7936,19 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F101" s="2">
         <v>5</v>
@@ -7852,7 +7957,7 @@
         <v>3</v>
       </c>
       <c r="H101" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I101" s="2">
         <v>0</v>
@@ -7870,19 +7975,19 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F102" s="2">
         <v>1.5</v>
@@ -7909,19 +8014,19 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F103" s="2">
         <v>4</v>
@@ -7930,7 +8035,7 @@
         <v>2.5</v>
       </c>
       <c r="H103" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I103" s="2">
         <v>0</v>
@@ -7948,19 +8053,19 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F104" s="2">
         <v>10</v>
@@ -7987,19 +8092,19 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F105" s="2">
         <v>3</v>
@@ -8026,19 +8131,19 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F106" s="2">
         <v>10</v>
@@ -8065,19 +8170,19 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F107" s="2">
         <v>3</v>
@@ -8104,19 +8209,19 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F108" s="2">
         <v>3</v>
@@ -8125,7 +8230,7 @@
         <v>1.5</v>
       </c>
       <c r="H108" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I108" s="2">
         <v>0</v>
@@ -8143,19 +8248,19 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F109" s="2">
         <v>5</v>
@@ -8164,7 +8269,7 @@
         <v>2.5</v>
       </c>
       <c r="H109" s="2">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I109" s="2">
         <v>0</v>
@@ -8182,19 +8287,19 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F110" s="2">
         <v>4</v>
@@ -8203,7 +8308,7 @@
         <v>2</v>
       </c>
       <c r="H110" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110" s="2">
         <v>0</v>
@@ -8221,19 +8326,19 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F111" s="2">
         <v>3</v>
@@ -8242,7 +8347,7 @@
         <v>1.5</v>
       </c>
       <c r="H111" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I111" s="2">
         <v>0</v>
@@ -8260,19 +8365,19 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F112" s="2">
         <v>2</v>
@@ -8281,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="H112" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I112" s="2">
         <v>0</v>
@@ -8299,19 +8404,19 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F113" s="2">
         <v>2</v>
@@ -8320,7 +8425,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I113" s="2">
         <v>0</v>
@@ -8338,19 +8443,19 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F114" s="2">
         <v>1</v>
@@ -8377,19 +8482,19 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F115" s="2">
         <v>3</v>
@@ -8416,19 +8521,19 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F116" s="2">
         <v>0</v>
@@ -8437,7 +8542,7 @@
         <v>3</v>
       </c>
       <c r="H116" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I116" s="2">
         <v>0</v>
@@ -8452,24 +8557,24 @@
         <v>3</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F117" s="2">
         <v>0</v>
@@ -8478,7 +8583,7 @@
         <v>3</v>
       </c>
       <c r="H117" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I117" s="2">
         <v>0</v>
@@ -8496,19 +8601,19 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C118" s="5">
         <v>11.1</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F118" s="2">
         <v>2</v>
@@ -8535,19 +8640,19 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C119" s="5">
         <v>11.2</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F119" s="2">
         <v>8</v>
@@ -8556,7 +8661,7 @@
         <v>4</v>
       </c>
       <c r="H119" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I119" s="2">
         <v>0</v>
@@ -8574,19 +8679,19 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C120" s="5">
         <v>11.3</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F120" s="2">
         <v>5</v>
@@ -8595,7 +8700,7 @@
         <v>2.5</v>
       </c>
       <c r="H120" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I120" s="2">
         <v>0</v>
@@ -8613,19 +8718,19 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C121" s="5">
         <v>11.4</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F121" s="2">
         <v>6</v>
@@ -8634,7 +8739,7 @@
         <v>2.5</v>
       </c>
       <c r="H121" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I121" s="2">
         <v>0</v>
@@ -8652,19 +8757,19 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C122" s="5">
         <v>11.5</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F122" s="2">
         <v>4</v>
@@ -8673,7 +8778,7 @@
         <v>2</v>
       </c>
       <c r="H122" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I122" s="2">
         <v>0</v>
@@ -8691,19 +8796,19 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C123" s="5">
         <v>11.6</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F123" s="2">
         <v>5</v>
@@ -8712,7 +8817,7 @@
         <v>3</v>
       </c>
       <c r="H123" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I123" s="2">
         <v>0</v>
@@ -8730,19 +8835,19 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C124" s="5">
         <v>11.7</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F124" s="2">
         <v>3</v>
@@ -8751,7 +8856,7 @@
         <v>2</v>
       </c>
       <c r="H124" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I124" s="2">
         <v>0</v>
@@ -8769,19 +8874,19 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C125" s="5">
         <v>11.8</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F125" s="2">
         <v>3</v>
@@ -8808,19 +8913,19 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C126" s="5">
         <v>11.9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F126" s="2">
         <v>2</v>
@@ -8847,19 +8952,19 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C127" s="5">
         <v>11.1</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F127" s="2">
         <v>3</v>
@@ -8868,7 +8973,7 @@
         <v>2.5</v>
       </c>
       <c r="H127" s="2">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I127" s="2">
         <v>0</v>
@@ -8886,19 +8991,19 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F128" s="2">
         <v>1.5</v>
@@ -8907,7 +9012,7 @@
         <v>0.8</v>
       </c>
       <c r="H128" s="2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I128" s="2">
         <v>0</v>
@@ -8925,19 +9030,19 @@
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F129" s="2">
         <v>8</v>
@@ -8964,19 +9069,19 @@
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F130" s="2">
         <v>102</v>
@@ -8985,7 +9090,7 @@
         <v>45</v>
       </c>
       <c r="H130" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I130" s="2">
         <v>0</v>
@@ -9003,19 +9108,19 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F131" s="2">
         <v>74</v>
@@ -9024,7 +9129,7 @@
         <v>32</v>
       </c>
       <c r="H131" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I131" s="2">
         <v>0</v>
@@ -9042,19 +9147,19 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F132" s="2">
         <v>46</v>
@@ -9063,7 +9168,7 @@
         <v>19</v>
       </c>
       <c r="H132" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I132" s="2">
         <v>0</v>
@@ -9081,19 +9186,19 @@
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F133" s="2">
         <v>46</v>
@@ -9102,7 +9207,7 @@
         <v>19</v>
       </c>
       <c r="H133" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I133" s="2">
         <v>0</v>
@@ -9120,19 +9225,19 @@
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F134" s="2">
         <v>46</v>
@@ -9141,7 +9246,7 @@
         <v>19</v>
       </c>
       <c r="H134" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I134" s="2">
         <v>0</v>
@@ -9159,19 +9264,19 @@
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F135" s="2">
         <v>152</v>
@@ -9180,7 +9285,7 @@
         <v>58</v>
       </c>
       <c r="H135" s="2">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="I135" s="2">
         <v>0</v>
@@ -9198,19 +9303,19 @@
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F136" s="2">
         <v>20</v>
@@ -9219,7 +9324,7 @@
         <v>16</v>
       </c>
       <c r="H136" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I136" s="2">
         <v>0</v>
@@ -9234,24 +9339,24 @@
         <v>16</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F137" s="2">
         <v>12</v>
@@ -9278,19 +9383,19 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F138" s="2">
         <v>8</v>
@@ -9299,7 +9404,7 @@
         <v>5</v>
       </c>
       <c r="H138" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I138" s="2">
         <v>0</v>
@@ -9317,19 +9422,19 @@
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F139" s="2">
         <v>10</v>
@@ -9356,19 +9461,19 @@
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F140" s="2">
         <v>12</v>
@@ -9377,7 +9482,7 @@
         <v>7</v>
       </c>
       <c r="H140" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I140" s="2">
         <v>0</v>
@@ -9395,19 +9500,19 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F141" s="2">
         <v>6</v>
@@ -9434,19 +9539,19 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F142" s="2">
         <v>4</v>
@@ -9455,7 +9560,7 @@
         <v>3.5</v>
       </c>
       <c r="H142" s="2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I142" s="2">
         <v>0</v>
@@ -9473,19 +9578,19 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F143" s="2">
         <v>3</v>
@@ -9512,19 +9617,19 @@
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F144" s="2">
         <v>5</v>
@@ -9533,7 +9638,7 @@
         <v>2.5</v>
       </c>
       <c r="H144" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I144" s="2">
         <v>1.5</v>
@@ -9548,24 +9653,24 @@
         <v>1.75</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F145" s="2">
         <v>4</v>
@@ -9574,7 +9679,7 @@
         <v>2</v>
       </c>
       <c r="H145" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I145" s="2">
         <v>1</v>
@@ -9592,19 +9697,19 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F146" s="2">
         <v>3</v>
@@ -9613,7 +9718,7 @@
         <v>1.5</v>
       </c>
       <c r="H146" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I146" s="2">
         <v>1.2</v>
@@ -9631,19 +9736,19 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F147" s="2">
         <v>3</v>
@@ -9652,7 +9757,7 @@
         <v>1.5</v>
       </c>
       <c r="H147" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I147" s="2">
         <v>0.9</v>
@@ -9670,19 +9775,19 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F148" s="2">
         <v>4</v>
@@ -9691,7 +9796,7 @@
         <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I148" s="2">
         <v>0</v>
@@ -9709,19 +9814,19 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F149" s="2">
         <v>2</v>
@@ -9730,7 +9835,7 @@
         <v>1.5</v>
       </c>
       <c r="H149" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I149" s="2">
         <v>0</v>
@@ -9748,19 +9853,19 @@
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F150" s="2">
         <v>3</v>
@@ -9769,7 +9874,7 @@
         <v>1.5</v>
       </c>
       <c r="H150" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I150" s="2">
         <v>0</v>
@@ -9787,19 +9892,19 @@
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F151" s="2">
         <v>6</v>
@@ -9826,19 +9931,19 @@
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F152" s="2">
         <v>1.5</v>
@@ -9847,7 +9952,7 @@
         <v>0.8</v>
       </c>
       <c r="H152" s="2">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I152" s="2">
         <v>0</v>
@@ -9865,19 +9970,19 @@
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F153" s="2">
         <v>1.5</v>
@@ -9886,7 +9991,7 @@
         <v>0.8</v>
       </c>
       <c r="H153" s="2">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I153" s="2">
         <v>0</v>
@@ -9904,19 +10009,19 @@
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F154" s="2">
         <v>1</v>
@@ -9943,19 +10048,19 @@
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F155" s="2">
         <v>3</v>
@@ -9964,7 +10069,7 @@
         <v>2</v>
       </c>
       <c r="H155" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I155" s="2">
         <v>0</v>
@@ -9982,19 +10087,19 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F156" s="2">
         <v>0</v>
@@ -10003,7 +10108,7 @@
         <v>2.5</v>
       </c>
       <c r="H156" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I156" s="2">
         <v>0</v>
@@ -10021,19 +10126,19 @@
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F157" s="2">
         <v>0</v>
@@ -10042,7 +10147,7 @@
         <v>2.5</v>
       </c>
       <c r="H157" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I157" s="2">
         <v>0</v>
@@ -10060,19 +10165,19 @@
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C158" s="5">
         <v>14.1</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F158" s="2">
         <v>1.5</v>
@@ -10081,7 +10186,7 @@
         <v>0.8</v>
       </c>
       <c r="H158" s="2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I158" s="2">
         <v>0</v>
@@ -10099,19 +10204,19 @@
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C159" s="5">
         <v>14.2</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F159" s="2">
         <v>2</v>
@@ -10135,24 +10240,24 @@
         <v>1</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C160" s="5">
         <v>14.3</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F160" s="2">
         <v>2</v>
@@ -10179,19 +10284,19 @@
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C161" s="5">
         <v>14.4</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F161" s="2">
         <v>4</v>
@@ -10218,19 +10323,19 @@
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C162" s="5">
         <v>14.5</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F162" s="2">
         <v>2</v>
@@ -10257,19 +10362,19 @@
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C163" s="5">
         <v>14.6</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F163" s="2">
         <v>3</v>
@@ -10296,19 +10401,19 @@
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C164" s="5">
         <v>14.7</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F164" s="2">
         <v>2</v>
@@ -10317,7 +10422,7 @@
         <v>1.5</v>
       </c>
       <c r="H164" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I164" s="2">
         <v>0</v>
@@ -10335,19 +10440,19 @@
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C165" s="5">
         <v>14.8</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F165" s="2">
         <v>2.5</v>
@@ -10356,7 +10461,7 @@
         <v>1.5</v>
       </c>
       <c r="H165" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I165" s="2">
         <v>0</v>
@@ -10374,19 +10479,19 @@
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C166" s="5">
         <v>14.9</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F166" s="2">
         <v>2</v>
@@ -10395,7 +10500,7 @@
         <v>2</v>
       </c>
       <c r="H166" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I166" s="2">
         <v>0</v>
@@ -10413,19 +10518,19 @@
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C167" s="5">
         <v>14.1</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F167" s="2">
         <v>3</v>
@@ -10434,7 +10539,7 @@
         <v>2.5</v>
       </c>
       <c r="H167" s="2">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I167" s="2">
         <v>0</v>
@@ -10452,19 +10557,19 @@
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F168" s="2">
         <v>1</v>
@@ -10473,7 +10578,7 @@
         <v>0.5</v>
       </c>
       <c r="H168" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I168" s="2">
         <v>0</v>
@@ -10491,19 +10596,19 @@
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F169" s="2">
         <v>4</v>
@@ -10530,19 +10635,19 @@
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F170" s="2">
         <v>36</v>
@@ -10551,7 +10656,7 @@
         <v>13.8</v>
       </c>
       <c r="H170" s="2">
-        <v>13.8</v>
+        <v>10</v>
       </c>
       <c r="I170" s="2">
         <v>0</v>
@@ -10569,19 +10674,19 @@
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F171" s="2">
         <v>26.5</v>
@@ -10590,7 +10695,7 @@
         <v>10</v>
       </c>
       <c r="H171" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I171" s="2">
         <v>0</v>
@@ -10608,19 +10713,19 @@
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F172" s="2">
         <v>17</v>
@@ -10629,7 +10734,7 @@
         <v>6.2</v>
       </c>
       <c r="H172" s="2">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="I172" s="2">
         <v>0</v>
@@ -10647,19 +10752,19 @@
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F173" s="2">
         <v>17</v>
@@ -10668,7 +10773,7 @@
         <v>6.2</v>
       </c>
       <c r="H173" s="2">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="I173" s="2">
         <v>0</v>
@@ -10686,19 +10791,19 @@
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F174" s="2">
         <v>17</v>
@@ -10707,7 +10812,7 @@
         <v>6.2</v>
       </c>
       <c r="H174" s="2">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="I174" s="2">
         <v>0</v>
@@ -10725,19 +10830,19 @@
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F175" s="2">
         <v>59</v>
@@ -10746,7 +10851,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="H175" s="2">
-        <v>20.399999999999999</v>
+        <v>10</v>
       </c>
       <c r="I175" s="2">
         <v>0</v>
@@ -10764,19 +10869,19 @@
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F176" s="2">
         <v>12</v>
@@ -10785,7 +10890,7 @@
         <v>10</v>
       </c>
       <c r="H176" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I176" s="2">
         <v>0</v>
@@ -10803,19 +10908,19 @@
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F177" s="2">
         <v>8</v>
@@ -10842,19 +10947,19 @@
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F178" s="2">
         <v>8</v>
@@ -10863,7 +10968,7 @@
         <v>5</v>
       </c>
       <c r="H178" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I178" s="2">
         <v>0</v>
@@ -10881,19 +10986,19 @@
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F179" s="2">
         <v>8</v>
@@ -10920,19 +11025,19 @@
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F180" s="2">
         <v>10</v>
@@ -10959,19 +11064,19 @@
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F181" s="2">
         <v>5</v>
@@ -10998,19 +11103,19 @@
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C182" s="5">
         <v>16.100000000000001</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F182" s="2">
         <v>6</v>
@@ -11019,7 +11124,7 @@
         <v>3.5</v>
       </c>
       <c r="H182" s="2">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I182" s="2">
         <v>0</v>
@@ -11037,19 +11142,19 @@
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C183" s="5">
         <v>16.2</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F183" s="2">
         <v>10</v>
@@ -11076,19 +11181,19 @@
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C184" s="5">
         <v>16.3</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F184" s="2">
         <v>8</v>
@@ -11115,19 +11220,19 @@
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C185" s="5">
         <v>16.399999999999999</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F185" s="2">
         <v>3</v>
@@ -11154,19 +11259,19 @@
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C186" s="5">
         <v>16.5</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F186" s="2">
         <v>10</v>
@@ -11175,7 +11280,7 @@
         <v>5</v>
       </c>
       <c r="H186" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I186" s="2">
         <v>0</v>
@@ -11193,19 +11298,19 @@
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C187" s="5">
         <v>16.600000000000001</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F187" s="2">
         <v>8</v>
@@ -11214,7 +11319,7 @@
         <v>4</v>
       </c>
       <c r="H187" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I187" s="2">
         <v>0</v>
@@ -11232,19 +11337,19 @@
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C188" s="5">
         <v>16.7</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F188" s="2">
         <v>4</v>
@@ -11271,19 +11376,19 @@
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C189" s="5">
         <v>16.8</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F189" s="2">
         <v>5</v>
@@ -11310,19 +11415,19 @@
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C190" s="5">
         <v>16.899999999999999</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F190" s="2">
         <v>5</v>
@@ -11349,19 +11454,19 @@
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C191" s="5">
         <v>16.100000000000001</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F191" s="2">
         <v>4</v>
@@ -11370,7 +11475,7 @@
         <v>3.5</v>
       </c>
       <c r="H191" s="2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I191" s="2">
         <v>0</v>
@@ -11388,19 +11493,19 @@
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C192" s="5">
         <v>16.11</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F192" s="2">
         <v>3</v>
@@ -11409,7 +11514,7 @@
         <v>2.5</v>
       </c>
       <c r="H192" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I192" s="2">
         <v>0</v>
@@ -11427,19 +11532,19 @@
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C193" s="5">
         <v>17.100000000000001</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F193" s="2">
         <v>5</v>
@@ -11466,19 +11571,19 @@
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C194" s="5">
         <v>17.2</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F194" s="2">
         <v>4</v>
@@ -11505,19 +11610,19 @@
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C195" s="5">
         <v>17.3</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F195" s="2">
         <v>4</v>
@@ -11526,7 +11631,7 @@
         <v>2</v>
       </c>
       <c r="H195" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I195" s="2">
         <v>0</v>
@@ -11544,19 +11649,19 @@
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C196" s="5">
         <v>17.399999999999999</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F196" s="2">
         <v>6</v>
@@ -11565,7 +11670,7 @@
         <v>3</v>
       </c>
       <c r="H196" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I196" s="2">
         <v>0</v>
@@ -11583,19 +11688,19 @@
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C197" s="5">
         <v>17.5</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F197" s="2">
         <v>3</v>
@@ -11604,7 +11709,7 @@
         <v>1.5</v>
       </c>
       <c r="H197" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I197" s="2">
         <v>0</v>
@@ -11622,19 +11727,19 @@
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C198" s="5">
         <v>17.600000000000001</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F198" s="2">
         <v>1.5</v>
@@ -11643,7 +11748,7 @@
         <v>0.8</v>
       </c>
       <c r="H198" s="2">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I198" s="2">
         <v>0</v>
@@ -11661,19 +11766,19 @@
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C199" s="5">
         <v>17.7</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F199" s="2">
         <v>4</v>
@@ -11682,7 +11787,7 @@
         <v>2.5</v>
       </c>
       <c r="H199" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I199" s="2">
         <v>0</v>
@@ -11700,19 +11805,19 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C200" s="5">
         <v>17.8</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F200" s="2">
         <v>3</v>
@@ -11739,19 +11844,19 @@
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C201" s="5">
         <v>17.899999999999999</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F201" s="2">
         <v>3</v>
@@ -11778,19 +11883,19 @@
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C202" s="5">
         <v>17.100000000000001</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F202" s="2">
         <v>2</v>
@@ -11817,19 +11922,19 @@
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C203" s="5">
         <v>17.11</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F203" s="2">
         <v>2</v>
@@ -11838,7 +11943,7 @@
         <v>1.5</v>
       </c>
       <c r="H203" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I203" s="2">
         <v>0</v>
@@ -11856,19 +11961,19 @@
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C204" s="5">
         <v>18.100000000000001</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F204" s="2">
         <v>5</v>
@@ -11895,19 +12000,19 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C205" s="5">
         <v>18.2</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F205" s="2">
         <v>4</v>
@@ -11934,19 +12039,19 @@
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C206" s="5">
         <v>18.3</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F206" s="2">
         <v>8</v>
@@ -11955,7 +12060,7 @@
         <v>4</v>
       </c>
       <c r="H206" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I206" s="2">
         <v>0</v>
@@ -11973,19 +12078,19 @@
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C207" s="5">
         <v>18.399999999999999</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F207" s="2">
         <v>3</v>
@@ -11994,7 +12099,7 @@
         <v>1.5</v>
       </c>
       <c r="H207" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I207" s="2">
         <v>0</v>
@@ -12012,19 +12117,19 @@
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C208" s="5">
         <v>18.5</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F208" s="2">
         <v>8</v>
@@ -12033,7 +12138,7 @@
         <v>4</v>
       </c>
       <c r="H208" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I208" s="2">
         <v>0</v>
@@ -12051,19 +12156,19 @@
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C209" s="5">
         <v>18.600000000000001</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F209" s="2">
         <v>6</v>
@@ -12090,19 +12195,19 @@
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C210" s="5">
         <v>18.7</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F210" s="2">
         <v>36</v>
@@ -12126,24 +12231,24 @@
         <v>14</v>
       </c>
       <c r="M210" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C211" s="5">
         <v>18.8</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F211" s="2">
         <v>3</v>
@@ -12152,7 +12257,7 @@
         <v>1.5</v>
       </c>
       <c r="H211" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I211" s="2">
         <v>0</v>
@@ -12170,19 +12275,19 @@
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C212" s="5">
         <v>18.899999999999999</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F212" s="2">
         <v>4</v>
@@ -12191,7 +12296,7 @@
         <v>2.5</v>
       </c>
       <c r="H212" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I212" s="2">
         <v>0</v>
@@ -12209,19 +12314,19 @@
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C213" s="5">
         <v>18.100000000000001</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F213" s="2">
         <v>4</v>
@@ -12248,19 +12353,19 @@
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C214" s="5">
         <v>18.11</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F214" s="2">
         <v>3</v>
@@ -12287,19 +12392,19 @@
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C215" s="5">
         <v>18.12</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F215" s="2">
         <v>2</v>
@@ -12326,19 +12431,19 @@
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C216" s="5">
         <v>19.100000000000001</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F216" s="2">
         <v>8</v>
@@ -12365,19 +12470,19 @@
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C217" s="5">
         <v>19.2</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F217" s="2">
         <v>5</v>
@@ -12404,19 +12509,19 @@
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C218" s="5">
         <v>19.3</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F218" s="2">
         <v>20</v>
@@ -12425,7 +12530,7 @@
         <v>10</v>
       </c>
       <c r="H218" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I218" s="2">
         <v>0</v>
@@ -12443,19 +12548,19 @@
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C219" s="5">
         <v>19.399999999999999</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F219" s="2">
         <v>8</v>
@@ -12482,19 +12587,19 @@
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C220" s="5">
         <v>19.5</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F220" s="2">
         <v>5</v>
@@ -12503,7 +12608,7 @@
         <v>2.5</v>
       </c>
       <c r="H220" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I220" s="2">
         <v>0</v>
@@ -12521,19 +12626,19 @@
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C221" s="5">
         <v>19.600000000000001</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F221" s="2">
         <v>5</v>
@@ -12542,7 +12647,7 @@
         <v>2.5</v>
       </c>
       <c r="H221" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I221" s="2">
         <v>0</v>
@@ -12560,19 +12665,19 @@
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C222" s="5">
         <v>19.7</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F222" s="2">
         <v>45</v>
@@ -12581,7 +12686,7 @@
         <v>18</v>
       </c>
       <c r="H222" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I222" s="2">
         <v>0</v>
@@ -12596,24 +12701,24 @@
         <v>18</v>
       </c>
       <c r="M222" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C223" s="5">
         <v>19.8</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F223" s="2">
         <v>6</v>
@@ -12622,7 +12727,7 @@
         <v>4</v>
       </c>
       <c r="H223" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I223" s="2">
         <v>0</v>
@@ -12640,19 +12745,19 @@
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C224" s="5">
         <v>19.899999999999999</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F224" s="2">
         <v>6</v>
@@ -12679,19 +12784,19 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C225" s="5">
         <v>19.100000000000001</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F225" s="2">
         <v>6</v>
@@ -12700,7 +12805,7 @@
         <v>4</v>
       </c>
       <c r="H225" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I225" s="2">
         <v>0</v>
@@ -12718,19 +12823,19 @@
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C226" s="5">
         <v>19.11</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F226" s="2">
         <v>5</v>
@@ -12739,7 +12844,7 @@
         <v>4</v>
       </c>
       <c r="H226" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I226" s="2">
         <v>0</v>
@@ -12757,19 +12862,19 @@
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C227" s="5">
         <v>19.12</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F227" s="2">
         <v>3</v>
@@ -12778,7 +12883,7 @@
         <v>2.5</v>
       </c>
       <c r="H227" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I227" s="2">
         <v>0</v>
@@ -12796,19 +12901,19 @@
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C228" s="5">
         <v>20.100000000000001</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F228" s="2">
         <v>10</v>
@@ -12835,19 +12940,19 @@
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C229" s="5">
         <v>20.2</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F229" s="2">
         <v>15</v>
@@ -12856,7 +12961,7 @@
         <v>8</v>
       </c>
       <c r="H229" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I229" s="2">
         <v>0</v>
@@ -12874,19 +12979,19 @@
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C230" s="5">
         <v>20.3</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F230" s="2">
         <v>8</v>
@@ -12913,19 +13018,19 @@
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C231" s="5">
         <v>20.399999999999999</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F231" s="2">
         <v>6</v>
@@ -12934,7 +13039,7 @@
         <v>4</v>
       </c>
       <c r="H231" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I231" s="2">
         <v>0</v>
@@ -12952,19 +13057,19 @@
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C232" s="5">
         <v>20.5</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F232" s="2">
         <v>4</v>
@@ -12973,7 +13078,7 @@
         <v>3</v>
       </c>
       <c r="H232" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I232" s="2">
         <v>0</v>
@@ -13010,24 +13115,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2">
         <v>199</v>
@@ -13044,7 +13149,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2">
         <v>1776.1</v>
@@ -13061,7 +13166,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3">
         <v>1975</v>
@@ -13093,244 +13198,244 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2">
         <v>0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C23" s="2"/>
     </row>
